--- a/VerveStacks_DZA_grids/SysSettings.xlsx
+++ b/VerveStacks_DZA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3897B245-B31F-4E6D-B318-DCACFF800934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334D94F5-48D0-4652-BC3D-7B004C4D12C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5780,7 +5780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1DD381-B194-432A-8A16-D335D061EE37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232C250D-6CFC-45FB-AF4E-4D5F5A951E43}">
   <dimension ref="B3:H310"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SysSettings.xlsx
+++ b/VerveStacks_DZA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334D94F5-48D0-4652-BC3D-7B004C4D12C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B616E2D0-9BFF-4C9A-8840-CCA9BD96E3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5780,7 +5780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232C250D-6CFC-45FB-AF4E-4D5F5A951E43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B218906-360E-46C3-B526-6A126B69DDAF}">
   <dimension ref="B3:H310"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SysSettings.xlsx
+++ b/VerveStacks_DZA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B616E2D0-9BFF-4C9A-8840-CCA9BD96E3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D46639-6FC2-460C-B2AE-C3D24F8E1F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3542" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="593">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1538,60 +1538,6 @@
     <t>lo</t>
   </si>
   <si>
-    <t>e_DZ10-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ10-220</t>
-  </si>
-  <si>
-    <t>e_DZ100-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ100-220</t>
-  </si>
-  <si>
-    <t>e_DZ101-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ101-220</t>
-  </si>
-  <si>
-    <t>e_DZ102-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ102-220</t>
-  </si>
-  <si>
-    <t>e_DZ103-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ103-220</t>
-  </si>
-  <si>
-    <t>e_DZ104-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ104-220</t>
-  </si>
-  <si>
-    <t>e_DZ105-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ105-220</t>
-  </si>
-  <si>
-    <t>e_DZ106-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ106-220</t>
-  </si>
-  <si>
-    <t>e_DZ107-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ107-220</t>
-  </si>
-  <si>
     <t>e_DZ108-400</t>
   </si>
   <si>
@@ -1604,168 +1550,30 @@
     <t>grid node -- DZ109-400</t>
   </si>
   <si>
-    <t>e_DZ11-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ11-220</t>
-  </si>
-  <si>
-    <t>e_DZ110-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ110-220</t>
-  </si>
-  <si>
-    <t>e_DZ111-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ111-220</t>
-  </si>
-  <si>
-    <t>e_DZ112-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ112-220</t>
-  </si>
-  <si>
     <t>e_DZ113-400</t>
   </si>
   <si>
     <t>grid node -- DZ113-400</t>
   </si>
   <si>
-    <t>e_DZ114-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ114-220</t>
-  </si>
-  <si>
-    <t>e_DZ115-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ115-220</t>
-  </si>
-  <si>
-    <t>e_DZ116-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ116-220</t>
-  </si>
-  <si>
-    <t>e_DZ117-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ117-220</t>
-  </si>
-  <si>
-    <t>e_DZ118-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ118-220</t>
-  </si>
-  <si>
-    <t>e_DZ119-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ119-220</t>
-  </si>
-  <si>
     <t>e_DZ12-400</t>
   </si>
   <si>
     <t>grid node -- DZ12-400</t>
   </si>
   <si>
-    <t>e_DZ120-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ120-220</t>
-  </si>
-  <si>
-    <t>e_DZ121-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ121-220</t>
-  </si>
-  <si>
-    <t>e_DZ122-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ122-220</t>
-  </si>
-  <si>
-    <t>e_DZ123-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ123-220</t>
-  </si>
-  <si>
-    <t>e_DZ124-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ124-220</t>
-  </si>
-  <si>
-    <t>e_DZ125-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ125-220</t>
-  </si>
-  <si>
-    <t>e_DZ126-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ126-220</t>
-  </si>
-  <si>
-    <t>e_DZ127-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ127-220</t>
-  </si>
-  <si>
     <t>e_DZ128-400</t>
   </si>
   <si>
     <t>grid node -- DZ128-400</t>
   </si>
   <si>
-    <t>e_DZ129-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ129-220</t>
-  </si>
-  <si>
     <t>e_DZ13-400</t>
   </si>
   <si>
     <t>grid node -- DZ13-400</t>
   </si>
   <si>
-    <t>e_DZ130-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ130-220</t>
-  </si>
-  <si>
-    <t>e_DZ131-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ131-220</t>
-  </si>
-  <si>
-    <t>e_DZ132-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ132-220</t>
-  </si>
-  <si>
-    <t>e_DZ133-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ133-220</t>
-  </si>
-  <si>
     <t>e_DZ134-400</t>
   </si>
   <si>
@@ -1778,504 +1586,42 @@
     <t>grid node -- DZ135-400</t>
   </si>
   <si>
-    <t>e_DZ136-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ136-220</t>
-  </si>
-  <si>
-    <t>e_DZ137-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ137-220</t>
-  </si>
-  <si>
-    <t>e_DZ138-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ138-220</t>
-  </si>
-  <si>
-    <t>e_DZ139-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ139-220</t>
-  </si>
-  <si>
     <t>e_DZ139-400</t>
   </si>
   <si>
     <t>grid node -- DZ139-400</t>
   </si>
   <si>
-    <t>e_DZ14-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ14-220</t>
-  </si>
-  <si>
-    <t>e_DZ140-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ140-220</t>
-  </si>
-  <si>
-    <t>e_DZ141-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ141-220</t>
-  </si>
-  <si>
-    <t>e_DZ142-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ142-220</t>
-  </si>
-  <si>
-    <t>e_DZ143-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ143-220</t>
-  </si>
-  <si>
-    <t>e_DZ144-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ144-220</t>
-  </si>
-  <si>
-    <t>e_DZ145-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ145-220</t>
-  </si>
-  <si>
-    <t>e_DZ146-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ146-220</t>
-  </si>
-  <si>
-    <t>e_DZ147-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ147-220</t>
-  </si>
-  <si>
-    <t>e_DZ148-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ148-220</t>
-  </si>
-  <si>
-    <t>e_DZ149-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ149-220</t>
-  </si>
-  <si>
-    <t>e_DZ15-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ15-220</t>
-  </si>
-  <si>
-    <t>e_DZ150-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ150-220</t>
-  </si>
-  <si>
-    <t>e_DZ151-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ151-220</t>
-  </si>
-  <si>
-    <t>e_DZ152-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ152-220</t>
-  </si>
-  <si>
-    <t>e_DZ153-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ153-220</t>
-  </si>
-  <si>
-    <t>e_DZ154-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ154-220</t>
-  </si>
-  <si>
-    <t>e_DZ155-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ155-220</t>
-  </si>
-  <si>
-    <t>e_DZ156-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ156-220</t>
-  </si>
-  <si>
-    <t>e_DZ157-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ157-220</t>
-  </si>
-  <si>
-    <t>e_DZ158-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ158-220</t>
-  </si>
-  <si>
-    <t>e_DZ159-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ159-220</t>
-  </si>
-  <si>
-    <t>e_DZ16-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ16-220</t>
-  </si>
-  <si>
-    <t>e_DZ160-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ160-220</t>
-  </si>
-  <si>
-    <t>e_DZ17-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ17-220</t>
-  </si>
-  <si>
-    <t>e_DZ18-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ18-220</t>
-  </si>
-  <si>
     <t>e_DZ18-400</t>
   </si>
   <si>
     <t>grid node -- DZ18-400</t>
   </si>
   <si>
-    <t>e_DZ19-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ19-220</t>
-  </si>
-  <si>
-    <t>e_DZ2-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ2-220</t>
-  </si>
-  <si>
     <t>e_DZ2-400</t>
   </si>
   <si>
     <t>grid node -- DZ2-400</t>
   </si>
   <si>
-    <t>e_DZ20-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ20-220</t>
-  </si>
-  <si>
-    <t>e_DZ21-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ21-220</t>
-  </si>
-  <si>
-    <t>e_DZ22-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ22-220</t>
-  </si>
-  <si>
-    <t>e_DZ23-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ23-220</t>
-  </si>
-  <si>
-    <t>e_DZ24-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ24-220</t>
-  </si>
-  <si>
-    <t>e_DZ25-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ25-220</t>
-  </si>
-  <si>
-    <t>e_DZ26-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ26-220</t>
-  </si>
-  <si>
-    <t>e_DZ27-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ27-220</t>
-  </si>
-  <si>
-    <t>e_DZ28-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ28-220</t>
-  </si>
-  <si>
-    <t>e_DZ29-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ29-220</t>
-  </si>
-  <si>
-    <t>e_DZ3-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ3-220</t>
-  </si>
-  <si>
-    <t>e_DZ30-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ30-220</t>
-  </si>
-  <si>
-    <t>e_DZ31-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ31-220</t>
-  </si>
-  <si>
-    <t>e_DZ32-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ32-220</t>
-  </si>
-  <si>
-    <t>e_DZ33-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ33-220</t>
-  </si>
-  <si>
-    <t>e_DZ34-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ34-220</t>
-  </si>
-  <si>
-    <t>e_DZ35-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ35-220</t>
-  </si>
-  <si>
-    <t>e_DZ36-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ36-220</t>
-  </si>
-  <si>
-    <t>e_DZ37-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ37-220</t>
-  </si>
-  <si>
-    <t>e_DZ38-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ38-220</t>
-  </si>
-  <si>
-    <t>e_DZ39-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ39-220</t>
-  </si>
-  <si>
-    <t>e_DZ4-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ4-220</t>
-  </si>
-  <si>
-    <t>e_DZ40-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ40-220</t>
-  </si>
-  <si>
-    <t>e_DZ42-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ42-220</t>
-  </si>
-  <si>
-    <t>e_DZ43-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ43-220</t>
-  </si>
-  <si>
-    <t>e_DZ44-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ44-220</t>
-  </si>
-  <si>
     <t>e_DZ45-400</t>
   </si>
   <si>
     <t>grid node -- DZ45-400</t>
   </si>
   <si>
-    <t>e_DZ46-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ46-220</t>
-  </si>
-  <si>
-    <t>e_DZ47-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ47-220</t>
-  </si>
-  <si>
-    <t>e_DZ48-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ48-220</t>
-  </si>
-  <si>
-    <t>e_DZ49-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ49-220</t>
-  </si>
-  <si>
-    <t>e_DZ5-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ5-220</t>
-  </si>
-  <si>
     <t>e_DZ50-400</t>
   </si>
   <si>
     <t>grid node -- DZ50-400</t>
   </si>
   <si>
-    <t>e_DZ51-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ51-220</t>
-  </si>
-  <si>
-    <t>e_DZ52-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ52-220</t>
-  </si>
-  <si>
-    <t>e_DZ53-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ53-220</t>
-  </si>
-  <si>
-    <t>e_DZ54-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ54-220</t>
-  </si>
-  <si>
-    <t>e_DZ55-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ55-220</t>
-  </si>
-  <si>
-    <t>e_DZ56-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ56-220</t>
-  </si>
-  <si>
-    <t>e_DZ57-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ57-220</t>
-  </si>
-  <si>
-    <t>e_DZ58-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ58-220</t>
-  </si>
-  <si>
-    <t>e_DZ59-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ59-220</t>
-  </si>
-  <si>
-    <t>e_DZ6-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ6-220</t>
-  </si>
-  <si>
-    <t>e_DZ60-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ60-220</t>
-  </si>
-  <si>
-    <t>e_DZ61-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ61-220</t>
-  </si>
-  <si>
-    <t>e_DZ62-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ62-220</t>
-  </si>
-  <si>
     <t>e_DZ63-400</t>
   </si>
   <si>
     <t>grid node -- DZ63-400</t>
   </si>
   <si>
-    <t>e_DZ64-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ64-220</t>
-  </si>
-  <si>
     <t>e_DZ65-400</t>
   </si>
   <si>
@@ -2294,912 +1640,126 @@
     <t>grid node -- DZ67-400</t>
   </si>
   <si>
-    <t>e_DZ69-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ69-220</t>
-  </si>
-  <si>
-    <t>e_DZ7-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ7-220</t>
-  </si>
-  <si>
-    <t>e_DZ70-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ70-220</t>
-  </si>
-  <si>
     <t>e_DZ71-400</t>
   </si>
   <si>
     <t>grid node -- DZ71-400</t>
   </si>
   <si>
-    <t>e_DZ72-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ72-220</t>
-  </si>
-  <si>
     <t>e_DZ72-400</t>
   </si>
   <si>
     <t>grid node -- DZ72-400</t>
   </si>
   <si>
-    <t>e_DZ73-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ73-220</t>
-  </si>
-  <si>
-    <t>e_DZ74-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ74-220</t>
-  </si>
-  <si>
-    <t>e_DZ75-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ75-220</t>
-  </si>
-  <si>
-    <t>e_DZ76-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ76-220</t>
-  </si>
-  <si>
-    <t>e_DZ77-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ77-220</t>
-  </si>
-  <si>
-    <t>e_DZ78-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ78-220</t>
-  </si>
-  <si>
-    <t>e_DZ79-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ79-220</t>
-  </si>
-  <si>
-    <t>e_DZ8-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ8-220</t>
-  </si>
-  <si>
-    <t>e_DZ80-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ80-220</t>
-  </si>
-  <si>
-    <t>e_DZ81-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ81-220</t>
-  </si>
-  <si>
-    <t>e_DZ82-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ82-220</t>
-  </si>
-  <si>
-    <t>e_DZ83-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ83-220</t>
-  </si>
-  <si>
-    <t>e_DZ84-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ84-220</t>
-  </si>
-  <si>
-    <t>e_DZ85-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ85-220</t>
-  </si>
-  <si>
-    <t>e_DZ86-225</t>
-  </si>
-  <si>
-    <t>grid node -- DZ86-225</t>
-  </si>
-  <si>
     <t>e_DZ87-400</t>
   </si>
   <si>
     <t>grid node -- DZ87-400</t>
   </si>
   <si>
-    <t>e_DZ88-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ88-220</t>
-  </si>
-  <si>
-    <t>e_DZ89-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ89-220</t>
-  </si>
-  <si>
-    <t>e_DZ9-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ9-220</t>
-  </si>
-  <si>
-    <t>e_DZ90-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ90-220</t>
-  </si>
-  <si>
-    <t>e_DZ91-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ91-220</t>
-  </si>
-  <si>
-    <t>e_DZ92-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ92-220</t>
-  </si>
-  <si>
-    <t>e_DZ93-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ93-220</t>
-  </si>
-  <si>
-    <t>e_DZ94-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ94-220</t>
-  </si>
-  <si>
-    <t>e_DZ95-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ95-220</t>
-  </si>
-  <si>
     <t>e_DZ96-400</t>
   </si>
   <si>
     <t>grid node -- DZ96-400</t>
   </si>
   <si>
-    <t>e_DZ97-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ97-220</t>
-  </si>
-  <si>
-    <t>e_DZ98-220</t>
-  </si>
-  <si>
-    <t>grid node -- DZ98-220</t>
-  </si>
-  <si>
     <t>e_DZ99-400</t>
   </si>
   <si>
     <t>grid node -- DZ99-400</t>
   </si>
   <si>
-    <t>e_w1031001205-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1031001205-220</t>
-  </si>
-  <si>
-    <t>e_w1031851533-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1031851533-220</t>
-  </si>
-  <si>
-    <t>e_w1033225557-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1033225557-220</t>
-  </si>
-  <si>
-    <t>e_w1033643187-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1033643187-220</t>
-  </si>
-  <si>
-    <t>e_w1037301407-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1037301407-220</t>
-  </si>
-  <si>
-    <t>e_w1056389360-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1056389360-220</t>
-  </si>
-  <si>
-    <t>e_w107574175-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/107574175-220</t>
-  </si>
-  <si>
-    <t>e_w107614291-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/107614291-220</t>
-  </si>
-  <si>
-    <t>e_w107649691-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/107649691-220</t>
-  </si>
-  <si>
-    <t>e_w107655510-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/107655510-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1167367928-220</t>
-  </si>
-  <si>
-    <t>e_w1303896195-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1303896195-220</t>
-  </si>
-  <si>
-    <t>e_w1354358035-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/1354358035-220</t>
-  </si>
-  <si>
     <t>e_w1377912118-400</t>
   </si>
   <si>
     <t>grid node -- way/1377912118-400</t>
   </si>
   <si>
-    <t>e_w172698243-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/172698243-220</t>
-  </si>
-  <si>
-    <t>e_w173534563-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173534563-220</t>
-  </si>
-  <si>
-    <t>e_w173670736-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173670736-220</t>
-  </si>
-  <si>
-    <t>e_w173670759-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173670759-220</t>
-  </si>
-  <si>
     <t>e_w173670759-400</t>
   </si>
   <si>
     <t>grid node -- way/173670759-400</t>
   </si>
   <si>
-    <t>e_w173677993-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173677993-220</t>
-  </si>
-  <si>
     <t>e_w173677993-400</t>
   </si>
   <si>
     <t>grid node -- way/173677993-400</t>
   </si>
   <si>
-    <t>e_w173682343-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173682343-220</t>
-  </si>
-  <si>
     <t>e_w173682343-400</t>
   </si>
   <si>
     <t>grid node -- way/173682343-400</t>
   </si>
   <si>
-    <t>e_w173805804-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173805804-220</t>
-  </si>
-  <si>
-    <t>e_w173808767-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173808767-220</t>
-  </si>
-  <si>
-    <t>e_w173985842-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/173985842-220</t>
-  </si>
-  <si>
-    <t>e_w174171686-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174171686-220</t>
-  </si>
-  <si>
-    <t>e_w174171691-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174171691-220</t>
-  </si>
-  <si>
-    <t>e_w174338940-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174338940-220</t>
-  </si>
-  <si>
-    <t>e_w174342293-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174342293-220</t>
-  </si>
-  <si>
-    <t>e_w174342295-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174342295-220</t>
-  </si>
-  <si>
-    <t>e_w174347010-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174347010-220</t>
-  </si>
-  <si>
-    <t>e_w174419698-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174419698-220</t>
-  </si>
-  <si>
-    <t>e_w174512286-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/174512286-220</t>
-  </si>
-  <si>
     <t>e_w174512286-400</t>
   </si>
   <si>
     <t>grid node -- way/174512286-400</t>
   </si>
   <si>
-    <t>e_w175176155-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/175176155-220</t>
-  </si>
-  <si>
-    <t>e_w175299043-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/175299043-220</t>
-  </si>
-  <si>
-    <t>e_w175343993-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/175343993-220</t>
-  </si>
-  <si>
-    <t>e_w176684982-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/176684982-220</t>
-  </si>
-  <si>
-    <t>e_w176932212-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/176932212-220</t>
-  </si>
-  <si>
     <t>e_w176932212-400</t>
   </si>
   <si>
     <t>grid node -- way/176932212-400</t>
   </si>
   <si>
-    <t>e_w176932220-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/176932220-220</t>
-  </si>
-  <si>
     <t>e_w176932220-400</t>
   </si>
   <si>
     <t>grid node -- way/176932220-400</t>
   </si>
   <si>
-    <t>e_w177004931-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/177004931-220</t>
-  </si>
-  <si>
     <t>e_w177004931-400</t>
   </si>
   <si>
     <t>grid node -- way/177004931-400</t>
   </si>
   <si>
-    <t>e_w177011339-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/177011339-220</t>
-  </si>
-  <si>
-    <t>e_w206847211-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/206847211-220</t>
-  </si>
-  <si>
-    <t>e_w217926708-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217926708-220</t>
-  </si>
-  <si>
-    <t>e_w217926710-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217926710-220</t>
-  </si>
-  <si>
-    <t>e_w217926711-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217926711-220</t>
-  </si>
-  <si>
-    <t>e_w217930454-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217930454-220</t>
-  </si>
-  <si>
-    <t>e_w217933343-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217933343-220</t>
-  </si>
-  <si>
-    <t>e_w217933346-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217933346-220</t>
-  </si>
-  <si>
-    <t>e_w217941443-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217941443-220</t>
-  </si>
-  <si>
-    <t>e_w217970970-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217970970-220</t>
-  </si>
-  <si>
-    <t>e_w217976993-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/217976993-220</t>
-  </si>
-  <si>
-    <t>e_w218114438-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/218114438-220</t>
-  </si>
-  <si>
-    <t>e_w221085150-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/221085150-220</t>
-  </si>
-  <si>
     <t>e_w221085150-400</t>
   </si>
   <si>
     <t>grid node -- way/221085150-400</t>
   </si>
   <si>
-    <t>e_w226392269-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226392269-220</t>
-  </si>
-  <si>
     <t>e_w226392269-400</t>
   </si>
   <si>
     <t>grid node -- way/226392269-400</t>
   </si>
   <si>
-    <t>e_w226879630-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226879630-220</t>
-  </si>
-  <si>
-    <t>e_w226886714-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226886714-220</t>
-  </si>
-  <si>
-    <t>e_w226912498-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226912498-220</t>
-  </si>
-  <si>
     <t>e_w226912498-400</t>
   </si>
   <si>
     <t>grid node -- way/226912498-400</t>
   </si>
   <si>
-    <t>e_w226918874-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226918874-220</t>
-  </si>
-  <si>
-    <t>e_w226922540-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226922540-220</t>
-  </si>
-  <si>
-    <t>e_w226985195-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/226985195-220</t>
-  </si>
-  <si>
-    <t>e_w227962923-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/227962923-220</t>
-  </si>
-  <si>
-    <t>e_w254853839-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/254853839-220</t>
-  </si>
-  <si>
-    <t>e_w261824495-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/261824495-220</t>
-  </si>
-  <si>
-    <t>e_w261824497-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/261824497-220</t>
-  </si>
-  <si>
-    <t>e_w262778513-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/262778513-220</t>
-  </si>
-  <si>
-    <t>e_w262778514-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/262778514-220</t>
-  </si>
-  <si>
-    <t>e_w262778515-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/262778515-220</t>
-  </si>
-  <si>
-    <t>e_w263135249-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/263135249-220</t>
-  </si>
-  <si>
-    <t>e_w292110924-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/292110924-220</t>
-  </si>
-  <si>
-    <t>e_w292487199-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/292487199-220</t>
-  </si>
-  <si>
-    <t>e_w293224489-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/293224489-220</t>
-  </si>
-  <si>
-    <t>e_w293467436-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/293467436-220</t>
-  </si>
-  <si>
-    <t>e_w294673631-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/294673631-220</t>
-  </si>
-  <si>
-    <t>e_w295277014-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/295277014-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/310510674-220</t>
-  </si>
-  <si>
-    <t>e_w312609390-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/312609390-220</t>
-  </si>
-  <si>
-    <t>e_w317645604-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/317645604-220</t>
-  </si>
-  <si>
-    <t>e_w317645796-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/317645796-220</t>
-  </si>
-  <si>
-    <t>e_w340227647-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/340227647-220</t>
-  </si>
-  <si>
-    <t>e_w359380463-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/359380463-220</t>
-  </si>
-  <si>
     <t>e_w359380463-400</t>
   </si>
   <si>
     <t>grid node -- way/359380463-400</t>
   </si>
   <si>
-    <t>e_w364421786-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/364421786-220</t>
-  </si>
-  <si>
-    <t>e_w365883660-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/365883660-220</t>
-  </si>
-  <si>
-    <t>e_w366187313-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/366187313-220</t>
-  </si>
-  <si>
-    <t>e_w371593266-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/371593266-220</t>
-  </si>
-  <si>
     <t>e_w377716686-400</t>
   </si>
   <si>
     <t>grid node -- way/377716686-400</t>
   </si>
   <si>
-    <t>e_w379387167-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/379387167-220</t>
-  </si>
-  <si>
-    <t>e_w380271836-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/380271836-220</t>
-  </si>
-  <si>
     <t>e_w380271836-400</t>
   </si>
   <si>
     <t>grid node -- way/380271836-400</t>
   </si>
   <si>
-    <t>e_w380645355-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/380645355-220</t>
-  </si>
-  <si>
-    <t>e_w380645355-225</t>
-  </si>
-  <si>
-    <t>grid node -- way/380645355-225</t>
-  </si>
-  <si>
-    <t>e_w381266482-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/381266482-220</t>
-  </si>
-  <si>
-    <t>e_w381355305-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/381355305-220</t>
-  </si>
-  <si>
-    <t>e_w381517754-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/381517754-220</t>
-  </si>
-  <si>
-    <t>e_w382497416-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/382497416-220</t>
-  </si>
-  <si>
-    <t>e_w383754584-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/383754584-220</t>
-  </si>
-  <si>
     <t>e_w383754584-400</t>
   </si>
   <si>
     <t>grid node -- way/383754584-400</t>
   </si>
   <si>
-    <t>e_w383755661-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/383755661-220</t>
-  </si>
-  <si>
-    <t>e_w384575278-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/384575278-220</t>
-  </si>
-  <si>
-    <t>e_w385608518-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/385608518-220</t>
-  </si>
-  <si>
-    <t>e_w387693359-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/387693359-220</t>
-  </si>
-  <si>
-    <t>e_w387845900-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/387845900-220</t>
-  </si>
-  <si>
-    <t>e_w390634433-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/390634433-220</t>
-  </si>
-  <si>
-    <t>e_w43843800-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/43843800-220</t>
-  </si>
-  <si>
-    <t>e_w464340115-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/464340115-220</t>
-  </si>
-  <si>
-    <t>e_w476360977-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/476360977-220</t>
-  </si>
-  <si>
-    <t>e_w533163474-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/533163474-220</t>
-  </si>
-  <si>
-    <t>e_w569616471-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/569616471-220</t>
-  </si>
-  <si>
     <t>e_w569616471-400</t>
   </si>
   <si>
@@ -3212,90 +1772,30 @@
     <t>grid node -- way/569616485-400</t>
   </si>
   <si>
-    <t>e_w569616494-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/569616494-220</t>
-  </si>
-  <si>
-    <t>e_w574859222-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/574859222-220</t>
-  </si>
-  <si>
     <t>e_w574859222-400</t>
   </si>
   <si>
     <t>grid node -- way/574859222-400</t>
   </si>
   <si>
-    <t>e_w575738414-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/575738414-220</t>
-  </si>
-  <si>
-    <t>e_w589902332-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/589902332-220</t>
-  </si>
-  <si>
-    <t>e_w610844609-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/610844609-220</t>
-  </si>
-  <si>
     <t>e_w610844609-400</t>
   </si>
   <si>
     <t>grid node -- way/610844609-400</t>
   </si>
   <si>
-    <t>e_w611220827-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/611220827-220</t>
-  </si>
-  <si>
     <t>e_w635672953-400</t>
   </si>
   <si>
     <t>grid node -- way/635672953-400</t>
   </si>
   <si>
-    <t>e_w637266751-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/637266751-220</t>
-  </si>
-  <si>
-    <t>e_w637288557-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/637288557-220</t>
-  </si>
-  <si>
-    <t>e_w694000747-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/694000747-220</t>
-  </si>
-  <si>
     <t>e_w694000747-400</t>
   </si>
   <si>
     <t>grid node -- way/694000747-400</t>
   </si>
   <si>
-    <t>e_w694000748-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/694000748-220</t>
-  </si>
-  <si>
     <t>e_w694011250-400</t>
   </si>
   <si>
@@ -3308,64 +1808,16 @@
     <t>grid node -- way/694011253-400</t>
   </si>
   <si>
-    <t>e_w694205380-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/694205380-220</t>
-  </si>
-  <si>
-    <t>e_w694205382-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/694205382-220</t>
-  </si>
-  <si>
-    <t>e_w720223304-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/720223304-220</t>
-  </si>
-  <si>
-    <t>e_w751040071-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/751040071-220</t>
-  </si>
-  <si>
     <t>e_w751040071-400</t>
   </si>
   <si>
     <t>grid node -- way/751040071-400</t>
   </si>
   <si>
-    <t>e_w833562295-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/833562295-220</t>
-  </si>
-  <si>
     <t>e_w833562295-400</t>
   </si>
   <si>
     <t>grid node -- way/833562295-400</t>
-  </si>
-  <si>
-    <t>e_w93235592-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/93235592-220</t>
-  </si>
-  <si>
-    <t>e_w936350097-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/936350097-220</t>
-  </si>
-  <si>
-    <t>e_w993660788-220</t>
-  </si>
-  <si>
-    <t>grid node -- way/993660788-220</t>
   </si>
 </sst>
 </file>
@@ -5780,8 +4232,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B218906-360E-46C3-B526-6A126B69DDAF}">
-  <dimension ref="B3:H310"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB85B8EC-E129-47CF-93E5-E6427F50AF9E}">
+  <dimension ref="B3:H52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
@@ -6913,5940 +5365,6 @@
         <v>498</v>
       </c>
       <c r="H52" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="s">
-        <v>593</v>
-      </c>
-      <c r="D53" t="s">
-        <v>594</v>
-      </c>
-      <c r="E53" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" t="s">
-        <v>498</v>
-      </c>
-      <c r="H53" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>595</v>
-      </c>
-      <c r="D54" t="s">
-        <v>596</v>
-      </c>
-      <c r="E54" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" t="s">
-        <v>35</v>
-      </c>
-      <c r="G54" t="s">
-        <v>498</v>
-      </c>
-      <c r="H54" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>597</v>
-      </c>
-      <c r="D55" t="s">
-        <v>598</v>
-      </c>
-      <c r="E55" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" t="s">
-        <v>35</v>
-      </c>
-      <c r="G55" t="s">
-        <v>498</v>
-      </c>
-      <c r="H55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>599</v>
-      </c>
-      <c r="D56" t="s">
-        <v>600</v>
-      </c>
-      <c r="E56" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" t="s">
-        <v>35</v>
-      </c>
-      <c r="G56" t="s">
-        <v>498</v>
-      </c>
-      <c r="H56" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>601</v>
-      </c>
-      <c r="D57" t="s">
-        <v>602</v>
-      </c>
-      <c r="E57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" t="s">
-        <v>498</v>
-      </c>
-      <c r="H57" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>603</v>
-      </c>
-      <c r="D58" t="s">
-        <v>604</v>
-      </c>
-      <c r="E58" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" t="s">
-        <v>35</v>
-      </c>
-      <c r="G58" t="s">
-        <v>498</v>
-      </c>
-      <c r="H58" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" t="s">
-        <v>605</v>
-      </c>
-      <c r="D59" t="s">
-        <v>606</v>
-      </c>
-      <c r="E59" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" t="s">
-        <v>35</v>
-      </c>
-      <c r="G59" t="s">
-        <v>498</v>
-      </c>
-      <c r="H59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
-      <c r="B60" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" t="s">
-        <v>607</v>
-      </c>
-      <c r="D60" t="s">
-        <v>608</v>
-      </c>
-      <c r="E60" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G60" t="s">
-        <v>498</v>
-      </c>
-      <c r="H60" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>609</v>
-      </c>
-      <c r="D61" t="s">
-        <v>610</v>
-      </c>
-      <c r="E61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G61" t="s">
-        <v>498</v>
-      </c>
-      <c r="H61" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>611</v>
-      </c>
-      <c r="D62" t="s">
-        <v>612</v>
-      </c>
-      <c r="E62" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" t="s">
-        <v>498</v>
-      </c>
-      <c r="H62" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>613</v>
-      </c>
-      <c r="D63" t="s">
-        <v>614</v>
-      </c>
-      <c r="E63" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" t="s">
-        <v>35</v>
-      </c>
-      <c r="G63" t="s">
-        <v>498</v>
-      </c>
-      <c r="H63" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>615</v>
-      </c>
-      <c r="D64" t="s">
-        <v>616</v>
-      </c>
-      <c r="E64" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" t="s">
-        <v>35</v>
-      </c>
-      <c r="G64" t="s">
-        <v>498</v>
-      </c>
-      <c r="H64" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8">
-      <c r="B65" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>617</v>
-      </c>
-      <c r="D65" t="s">
-        <v>618</v>
-      </c>
-      <c r="E65" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" t="s">
-        <v>35</v>
-      </c>
-      <c r="G65" t="s">
-        <v>498</v>
-      </c>
-      <c r="H65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="B66" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" t="s">
-        <v>619</v>
-      </c>
-      <c r="D66" t="s">
-        <v>620</v>
-      </c>
-      <c r="E66" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" t="s">
-        <v>35</v>
-      </c>
-      <c r="G66" t="s">
-        <v>498</v>
-      </c>
-      <c r="H66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
-      <c r="B67" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" t="s">
-        <v>621</v>
-      </c>
-      <c r="D67" t="s">
-        <v>622</v>
-      </c>
-      <c r="E67" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" t="s">
-        <v>35</v>
-      </c>
-      <c r="G67" t="s">
-        <v>498</v>
-      </c>
-      <c r="H67" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8">
-      <c r="B68" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" t="s">
-        <v>623</v>
-      </c>
-      <c r="D68" t="s">
-        <v>624</v>
-      </c>
-      <c r="E68" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" t="s">
-        <v>35</v>
-      </c>
-      <c r="G68" t="s">
-        <v>498</v>
-      </c>
-      <c r="H68" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" t="s">
-        <v>625</v>
-      </c>
-      <c r="D69" t="s">
-        <v>626</v>
-      </c>
-      <c r="E69" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" t="s">
-        <v>35</v>
-      </c>
-      <c r="G69" t="s">
-        <v>498</v>
-      </c>
-      <c r="H69" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8">
-      <c r="B70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" t="s">
-        <v>627</v>
-      </c>
-      <c r="D70" t="s">
-        <v>628</v>
-      </c>
-      <c r="E70" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70" t="s">
-        <v>35</v>
-      </c>
-      <c r="G70" t="s">
-        <v>498</v>
-      </c>
-      <c r="H70" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
-      <c r="B71" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" t="s">
-        <v>629</v>
-      </c>
-      <c r="D71" t="s">
-        <v>630</v>
-      </c>
-      <c r="E71" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" t="s">
-        <v>35</v>
-      </c>
-      <c r="G71" t="s">
-        <v>498</v>
-      </c>
-      <c r="H71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8">
-      <c r="B72" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" t="s">
-        <v>631</v>
-      </c>
-      <c r="D72" t="s">
-        <v>632</v>
-      </c>
-      <c r="E72" t="s">
-        <v>25</v>
-      </c>
-      <c r="F72" t="s">
-        <v>35</v>
-      </c>
-      <c r="G72" t="s">
-        <v>498</v>
-      </c>
-      <c r="H72" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" t="s">
-        <v>633</v>
-      </c>
-      <c r="D73" t="s">
-        <v>634</v>
-      </c>
-      <c r="E73" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" t="s">
-        <v>35</v>
-      </c>
-      <c r="G73" t="s">
-        <v>498</v>
-      </c>
-      <c r="H73" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="B74" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" t="s">
-        <v>635</v>
-      </c>
-      <c r="D74" t="s">
-        <v>636</v>
-      </c>
-      <c r="E74" t="s">
-        <v>25</v>
-      </c>
-      <c r="F74" t="s">
-        <v>35</v>
-      </c>
-      <c r="G74" t="s">
-        <v>498</v>
-      </c>
-      <c r="H74" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8">
-      <c r="B75" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75" t="s">
-        <v>637</v>
-      </c>
-      <c r="D75" t="s">
-        <v>638</v>
-      </c>
-      <c r="E75" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75" t="s">
-        <v>35</v>
-      </c>
-      <c r="G75" t="s">
-        <v>498</v>
-      </c>
-      <c r="H75" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" t="s">
-        <v>639</v>
-      </c>
-      <c r="D76" t="s">
-        <v>640</v>
-      </c>
-      <c r="E76" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" t="s">
-        <v>35</v>
-      </c>
-      <c r="G76" t="s">
-        <v>498</v>
-      </c>
-      <c r="H76" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8">
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" t="s">
-        <v>641</v>
-      </c>
-      <c r="D77" t="s">
-        <v>642</v>
-      </c>
-      <c r="E77" t="s">
-        <v>25</v>
-      </c>
-      <c r="F77" t="s">
-        <v>35</v>
-      </c>
-      <c r="G77" t="s">
-        <v>498</v>
-      </c>
-      <c r="H77" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8">
-      <c r="B78" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78" t="s">
-        <v>643</v>
-      </c>
-      <c r="D78" t="s">
-        <v>644</v>
-      </c>
-      <c r="E78" t="s">
-        <v>25</v>
-      </c>
-      <c r="F78" t="s">
-        <v>35</v>
-      </c>
-      <c r="G78" t="s">
-        <v>498</v>
-      </c>
-      <c r="H78" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8">
-      <c r="B79" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" t="s">
-        <v>645</v>
-      </c>
-      <c r="D79" t="s">
-        <v>646</v>
-      </c>
-      <c r="E79" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" t="s">
-        <v>35</v>
-      </c>
-      <c r="G79" t="s">
-        <v>498</v>
-      </c>
-      <c r="H79" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8">
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>647</v>
-      </c>
-      <c r="D80" t="s">
-        <v>648</v>
-      </c>
-      <c r="E80" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" t="s">
-        <v>35</v>
-      </c>
-      <c r="G80" t="s">
-        <v>498</v>
-      </c>
-      <c r="H80" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
-      <c r="B81" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" t="s">
-        <v>649</v>
-      </c>
-      <c r="D81" t="s">
-        <v>650</v>
-      </c>
-      <c r="E81" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" t="s">
-        <v>35</v>
-      </c>
-      <c r="G81" t="s">
-        <v>498</v>
-      </c>
-      <c r="H81" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
-      <c r="B82" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" t="s">
-        <v>651</v>
-      </c>
-      <c r="D82" t="s">
-        <v>652</v>
-      </c>
-      <c r="E82" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" t="s">
-        <v>35</v>
-      </c>
-      <c r="G82" t="s">
-        <v>498</v>
-      </c>
-      <c r="H82" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8">
-      <c r="B83" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" t="s">
-        <v>653</v>
-      </c>
-      <c r="D83" t="s">
-        <v>654</v>
-      </c>
-      <c r="E83" t="s">
-        <v>25</v>
-      </c>
-      <c r="F83" t="s">
-        <v>35</v>
-      </c>
-      <c r="G83" t="s">
-        <v>498</v>
-      </c>
-      <c r="H83" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8">
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" t="s">
-        <v>655</v>
-      </c>
-      <c r="D84" t="s">
-        <v>656</v>
-      </c>
-      <c r="E84" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" t="s">
-        <v>35</v>
-      </c>
-      <c r="G84" t="s">
-        <v>498</v>
-      </c>
-      <c r="H84" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
-      <c r="B85" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" t="s">
-        <v>657</v>
-      </c>
-      <c r="D85" t="s">
-        <v>658</v>
-      </c>
-      <c r="E85" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G85" t="s">
-        <v>498</v>
-      </c>
-      <c r="H85" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8">
-      <c r="B86" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" t="s">
-        <v>659</v>
-      </c>
-      <c r="D86" t="s">
-        <v>660</v>
-      </c>
-      <c r="E86" t="s">
-        <v>25</v>
-      </c>
-      <c r="F86" t="s">
-        <v>35</v>
-      </c>
-      <c r="G86" t="s">
-        <v>498</v>
-      </c>
-      <c r="H86" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8">
-      <c r="B87" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" t="s">
-        <v>661</v>
-      </c>
-      <c r="D87" t="s">
-        <v>662</v>
-      </c>
-      <c r="E87" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87" t="s">
-        <v>35</v>
-      </c>
-      <c r="G87" t="s">
-        <v>498</v>
-      </c>
-      <c r="H87" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
-      <c r="B88" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" t="s">
-        <v>663</v>
-      </c>
-      <c r="D88" t="s">
-        <v>664</v>
-      </c>
-      <c r="E88" t="s">
-        <v>25</v>
-      </c>
-      <c r="F88" t="s">
-        <v>35</v>
-      </c>
-      <c r="G88" t="s">
-        <v>498</v>
-      </c>
-      <c r="H88" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8">
-      <c r="B89" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" t="s">
-        <v>665</v>
-      </c>
-      <c r="D89" t="s">
-        <v>666</v>
-      </c>
-      <c r="E89" t="s">
-        <v>25</v>
-      </c>
-      <c r="F89" t="s">
-        <v>35</v>
-      </c>
-      <c r="G89" t="s">
-        <v>498</v>
-      </c>
-      <c r="H89" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8">
-      <c r="B90" t="s">
-        <v>17</v>
-      </c>
-      <c r="C90" t="s">
-        <v>667</v>
-      </c>
-      <c r="D90" t="s">
-        <v>668</v>
-      </c>
-      <c r="E90" t="s">
-        <v>25</v>
-      </c>
-      <c r="F90" t="s">
-        <v>35</v>
-      </c>
-      <c r="G90" t="s">
-        <v>498</v>
-      </c>
-      <c r="H90" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8">
-      <c r="B91" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" t="s">
-        <v>669</v>
-      </c>
-      <c r="D91" t="s">
-        <v>670</v>
-      </c>
-      <c r="E91" t="s">
-        <v>25</v>
-      </c>
-      <c r="F91" t="s">
-        <v>35</v>
-      </c>
-      <c r="G91" t="s">
-        <v>498</v>
-      </c>
-      <c r="H91" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8">
-      <c r="B92" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
-        <v>671</v>
-      </c>
-      <c r="D92" t="s">
-        <v>672</v>
-      </c>
-      <c r="E92" t="s">
-        <v>25</v>
-      </c>
-      <c r="F92" t="s">
-        <v>35</v>
-      </c>
-      <c r="G92" t="s">
-        <v>498</v>
-      </c>
-      <c r="H92" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8">
-      <c r="B93" t="s">
-        <v>17</v>
-      </c>
-      <c r="C93" t="s">
-        <v>673</v>
-      </c>
-      <c r="D93" t="s">
-        <v>674</v>
-      </c>
-      <c r="E93" t="s">
-        <v>25</v>
-      </c>
-      <c r="F93" t="s">
-        <v>35</v>
-      </c>
-      <c r="G93" t="s">
-        <v>498</v>
-      </c>
-      <c r="H93" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" t="s">
-        <v>675</v>
-      </c>
-      <c r="D94" t="s">
-        <v>676</v>
-      </c>
-      <c r="E94" t="s">
-        <v>25</v>
-      </c>
-      <c r="F94" t="s">
-        <v>35</v>
-      </c>
-      <c r="G94" t="s">
-        <v>498</v>
-      </c>
-      <c r="H94" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8">
-      <c r="B95" t="s">
-        <v>17</v>
-      </c>
-      <c r="C95" t="s">
-        <v>677</v>
-      </c>
-      <c r="D95" t="s">
-        <v>678</v>
-      </c>
-      <c r="E95" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" t="s">
-        <v>35</v>
-      </c>
-      <c r="G95" t="s">
-        <v>498</v>
-      </c>
-      <c r="H95" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8">
-      <c r="B96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C96" t="s">
-        <v>679</v>
-      </c>
-      <c r="D96" t="s">
-        <v>680</v>
-      </c>
-      <c r="E96" t="s">
-        <v>25</v>
-      </c>
-      <c r="F96" t="s">
-        <v>35</v>
-      </c>
-      <c r="G96" t="s">
-        <v>498</v>
-      </c>
-      <c r="H96" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8">
-      <c r="B97" t="s">
-        <v>17</v>
-      </c>
-      <c r="C97" t="s">
-        <v>681</v>
-      </c>
-      <c r="D97" t="s">
-        <v>682</v>
-      </c>
-      <c r="E97" t="s">
-        <v>25</v>
-      </c>
-      <c r="F97" t="s">
-        <v>35</v>
-      </c>
-      <c r="G97" t="s">
-        <v>498</v>
-      </c>
-      <c r="H97" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="98" spans="2:8">
-      <c r="B98" t="s">
-        <v>17</v>
-      </c>
-      <c r="C98" t="s">
-        <v>683</v>
-      </c>
-      <c r="D98" t="s">
-        <v>684</v>
-      </c>
-      <c r="E98" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" t="s">
-        <v>35</v>
-      </c>
-      <c r="G98" t="s">
-        <v>498</v>
-      </c>
-      <c r="H98" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8">
-      <c r="B99" t="s">
-        <v>17</v>
-      </c>
-      <c r="C99" t="s">
-        <v>685</v>
-      </c>
-      <c r="D99" t="s">
-        <v>686</v>
-      </c>
-      <c r="E99" t="s">
-        <v>25</v>
-      </c>
-      <c r="F99" t="s">
-        <v>35</v>
-      </c>
-      <c r="G99" t="s">
-        <v>498</v>
-      </c>
-      <c r="H99" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8">
-      <c r="B100" t="s">
-        <v>17</v>
-      </c>
-      <c r="C100" t="s">
-        <v>687</v>
-      </c>
-      <c r="D100" t="s">
-        <v>688</v>
-      </c>
-      <c r="E100" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100" t="s">
-        <v>35</v>
-      </c>
-      <c r="G100" t="s">
-        <v>498</v>
-      </c>
-      <c r="H100" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="101" spans="2:8">
-      <c r="B101" t="s">
-        <v>17</v>
-      </c>
-      <c r="C101" t="s">
-        <v>689</v>
-      </c>
-      <c r="D101" t="s">
-        <v>690</v>
-      </c>
-      <c r="E101" t="s">
-        <v>25</v>
-      </c>
-      <c r="F101" t="s">
-        <v>35</v>
-      </c>
-      <c r="G101" t="s">
-        <v>498</v>
-      </c>
-      <c r="H101" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="102" spans="2:8">
-      <c r="B102" t="s">
-        <v>17</v>
-      </c>
-      <c r="C102" t="s">
-        <v>691</v>
-      </c>
-      <c r="D102" t="s">
-        <v>692</v>
-      </c>
-      <c r="E102" t="s">
-        <v>25</v>
-      </c>
-      <c r="F102" t="s">
-        <v>35</v>
-      </c>
-      <c r="G102" t="s">
-        <v>498</v>
-      </c>
-      <c r="H102" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8">
-      <c r="B103" t="s">
-        <v>17</v>
-      </c>
-      <c r="C103" t="s">
-        <v>693</v>
-      </c>
-      <c r="D103" t="s">
-        <v>694</v>
-      </c>
-      <c r="E103" t="s">
-        <v>25</v>
-      </c>
-      <c r="F103" t="s">
-        <v>35</v>
-      </c>
-      <c r="G103" t="s">
-        <v>498</v>
-      </c>
-      <c r="H103" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="104" spans="2:8">
-      <c r="B104" t="s">
-        <v>17</v>
-      </c>
-      <c r="C104" t="s">
-        <v>695</v>
-      </c>
-      <c r="D104" t="s">
-        <v>696</v>
-      </c>
-      <c r="E104" t="s">
-        <v>25</v>
-      </c>
-      <c r="F104" t="s">
-        <v>35</v>
-      </c>
-      <c r="G104" t="s">
-        <v>498</v>
-      </c>
-      <c r="H104" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="105" spans="2:8">
-      <c r="B105" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" t="s">
-        <v>697</v>
-      </c>
-      <c r="D105" t="s">
-        <v>698</v>
-      </c>
-      <c r="E105" t="s">
-        <v>25</v>
-      </c>
-      <c r="F105" t="s">
-        <v>35</v>
-      </c>
-      <c r="G105" t="s">
-        <v>498</v>
-      </c>
-      <c r="H105" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8">
-      <c r="B106" t="s">
-        <v>17</v>
-      </c>
-      <c r="C106" t="s">
-        <v>699</v>
-      </c>
-      <c r="D106" t="s">
-        <v>700</v>
-      </c>
-      <c r="E106" t="s">
-        <v>25</v>
-      </c>
-      <c r="F106" t="s">
-        <v>35</v>
-      </c>
-      <c r="G106" t="s">
-        <v>498</v>
-      </c>
-      <c r="H106" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8">
-      <c r="B107" t="s">
-        <v>17</v>
-      </c>
-      <c r="C107" t="s">
-        <v>701</v>
-      </c>
-      <c r="D107" t="s">
-        <v>702</v>
-      </c>
-      <c r="E107" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" t="s">
-        <v>35</v>
-      </c>
-      <c r="G107" t="s">
-        <v>498</v>
-      </c>
-      <c r="H107" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8">
-      <c r="B108" t="s">
-        <v>17</v>
-      </c>
-      <c r="C108" t="s">
-        <v>703</v>
-      </c>
-      <c r="D108" t="s">
-        <v>704</v>
-      </c>
-      <c r="E108" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" t="s">
-        <v>35</v>
-      </c>
-      <c r="G108" t="s">
-        <v>498</v>
-      </c>
-      <c r="H108" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8">
-      <c r="B109" t="s">
-        <v>17</v>
-      </c>
-      <c r="C109" t="s">
-        <v>705</v>
-      </c>
-      <c r="D109" t="s">
-        <v>706</v>
-      </c>
-      <c r="E109" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" t="s">
-        <v>35</v>
-      </c>
-      <c r="G109" t="s">
-        <v>498</v>
-      </c>
-      <c r="H109" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8">
-      <c r="B110" t="s">
-        <v>17</v>
-      </c>
-      <c r="C110" t="s">
-        <v>707</v>
-      </c>
-      <c r="D110" t="s">
-        <v>708</v>
-      </c>
-      <c r="E110" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" t="s">
-        <v>35</v>
-      </c>
-      <c r="G110" t="s">
-        <v>498</v>
-      </c>
-      <c r="H110" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="111" spans="2:8">
-      <c r="B111" t="s">
-        <v>17</v>
-      </c>
-      <c r="C111" t="s">
-        <v>709</v>
-      </c>
-      <c r="D111" t="s">
-        <v>710</v>
-      </c>
-      <c r="E111" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" t="s">
-        <v>35</v>
-      </c>
-      <c r="G111" t="s">
-        <v>498</v>
-      </c>
-      <c r="H111" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8">
-      <c r="B112" t="s">
-        <v>17</v>
-      </c>
-      <c r="C112" t="s">
-        <v>711</v>
-      </c>
-      <c r="D112" t="s">
-        <v>712</v>
-      </c>
-      <c r="E112" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" t="s">
-        <v>35</v>
-      </c>
-      <c r="G112" t="s">
-        <v>498</v>
-      </c>
-      <c r="H112" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="113" spans="2:8">
-      <c r="B113" t="s">
-        <v>17</v>
-      </c>
-      <c r="C113" t="s">
-        <v>713</v>
-      </c>
-      <c r="D113" t="s">
-        <v>714</v>
-      </c>
-      <c r="E113" t="s">
-        <v>25</v>
-      </c>
-      <c r="F113" t="s">
-        <v>35</v>
-      </c>
-      <c r="G113" t="s">
-        <v>498</v>
-      </c>
-      <c r="H113" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8">
-      <c r="B114" t="s">
-        <v>17</v>
-      </c>
-      <c r="C114" t="s">
-        <v>715</v>
-      </c>
-      <c r="D114" t="s">
-        <v>716</v>
-      </c>
-      <c r="E114" t="s">
-        <v>25</v>
-      </c>
-      <c r="F114" t="s">
-        <v>35</v>
-      </c>
-      <c r="G114" t="s">
-        <v>498</v>
-      </c>
-      <c r="H114" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8">
-      <c r="B115" t="s">
-        <v>17</v>
-      </c>
-      <c r="C115" t="s">
-        <v>717</v>
-      </c>
-      <c r="D115" t="s">
-        <v>718</v>
-      </c>
-      <c r="E115" t="s">
-        <v>25</v>
-      </c>
-      <c r="F115" t="s">
-        <v>35</v>
-      </c>
-      <c r="G115" t="s">
-        <v>498</v>
-      </c>
-      <c r="H115" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="116" spans="2:8">
-      <c r="B116" t="s">
-        <v>17</v>
-      </c>
-      <c r="C116" t="s">
-        <v>719</v>
-      </c>
-      <c r="D116" t="s">
-        <v>720</v>
-      </c>
-      <c r="E116" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" t="s">
-        <v>35</v>
-      </c>
-      <c r="G116" t="s">
-        <v>498</v>
-      </c>
-      <c r="H116" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="117" spans="2:8">
-      <c r="B117" t="s">
-        <v>17</v>
-      </c>
-      <c r="C117" t="s">
-        <v>721</v>
-      </c>
-      <c r="D117" t="s">
-        <v>722</v>
-      </c>
-      <c r="E117" t="s">
-        <v>25</v>
-      </c>
-      <c r="F117" t="s">
-        <v>35</v>
-      </c>
-      <c r="G117" t="s">
-        <v>498</v>
-      </c>
-      <c r="H117" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="118" spans="2:8">
-      <c r="B118" t="s">
-        <v>17</v>
-      </c>
-      <c r="C118" t="s">
-        <v>723</v>
-      </c>
-      <c r="D118" t="s">
-        <v>724</v>
-      </c>
-      <c r="E118" t="s">
-        <v>25</v>
-      </c>
-      <c r="F118" t="s">
-        <v>35</v>
-      </c>
-      <c r="G118" t="s">
-        <v>498</v>
-      </c>
-      <c r="H118" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="119" spans="2:8">
-      <c r="B119" t="s">
-        <v>17</v>
-      </c>
-      <c r="C119" t="s">
-        <v>725</v>
-      </c>
-      <c r="D119" t="s">
-        <v>726</v>
-      </c>
-      <c r="E119" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" t="s">
-        <v>35</v>
-      </c>
-      <c r="G119" t="s">
-        <v>498</v>
-      </c>
-      <c r="H119" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8">
-      <c r="B120" t="s">
-        <v>17</v>
-      </c>
-      <c r="C120" t="s">
-        <v>727</v>
-      </c>
-      <c r="D120" t="s">
-        <v>728</v>
-      </c>
-      <c r="E120" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" t="s">
-        <v>35</v>
-      </c>
-      <c r="G120" t="s">
-        <v>498</v>
-      </c>
-      <c r="H120" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8">
-      <c r="B121" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" t="s">
-        <v>729</v>
-      </c>
-      <c r="D121" t="s">
-        <v>730</v>
-      </c>
-      <c r="E121" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" t="s">
-        <v>35</v>
-      </c>
-      <c r="G121" t="s">
-        <v>498</v>
-      </c>
-      <c r="H121" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8">
-      <c r="B122" t="s">
-        <v>17</v>
-      </c>
-      <c r="C122" t="s">
-        <v>731</v>
-      </c>
-      <c r="D122" t="s">
-        <v>732</v>
-      </c>
-      <c r="E122" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" t="s">
-        <v>35</v>
-      </c>
-      <c r="G122" t="s">
-        <v>498</v>
-      </c>
-      <c r="H122" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="123" spans="2:8">
-      <c r="B123" t="s">
-        <v>17</v>
-      </c>
-      <c r="C123" t="s">
-        <v>733</v>
-      </c>
-      <c r="D123" t="s">
-        <v>734</v>
-      </c>
-      <c r="E123" t="s">
-        <v>25</v>
-      </c>
-      <c r="F123" t="s">
-        <v>35</v>
-      </c>
-      <c r="G123" t="s">
-        <v>498</v>
-      </c>
-      <c r="H123" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="124" spans="2:8">
-      <c r="B124" t="s">
-        <v>17</v>
-      </c>
-      <c r="C124" t="s">
-        <v>735</v>
-      </c>
-      <c r="D124" t="s">
-        <v>736</v>
-      </c>
-      <c r="E124" t="s">
-        <v>25</v>
-      </c>
-      <c r="F124" t="s">
-        <v>35</v>
-      </c>
-      <c r="G124" t="s">
-        <v>498</v>
-      </c>
-      <c r="H124" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="125" spans="2:8">
-      <c r="B125" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" t="s">
-        <v>737</v>
-      </c>
-      <c r="D125" t="s">
-        <v>738</v>
-      </c>
-      <c r="E125" t="s">
-        <v>25</v>
-      </c>
-      <c r="F125" t="s">
-        <v>35</v>
-      </c>
-      <c r="G125" t="s">
-        <v>498</v>
-      </c>
-      <c r="H125" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="126" spans="2:8">
-      <c r="B126" t="s">
-        <v>17</v>
-      </c>
-      <c r="C126" t="s">
-        <v>739</v>
-      </c>
-      <c r="D126" t="s">
-        <v>740</v>
-      </c>
-      <c r="E126" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" t="s">
-        <v>35</v>
-      </c>
-      <c r="G126" t="s">
-        <v>498</v>
-      </c>
-      <c r="H126" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="127" spans="2:8">
-      <c r="B127" t="s">
-        <v>17</v>
-      </c>
-      <c r="C127" t="s">
-        <v>741</v>
-      </c>
-      <c r="D127" t="s">
-        <v>742</v>
-      </c>
-      <c r="E127" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" t="s">
-        <v>35</v>
-      </c>
-      <c r="G127" t="s">
-        <v>498</v>
-      </c>
-      <c r="H127" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="128" spans="2:8">
-      <c r="B128" t="s">
-        <v>17</v>
-      </c>
-      <c r="C128" t="s">
-        <v>743</v>
-      </c>
-      <c r="D128" t="s">
-        <v>744</v>
-      </c>
-      <c r="E128" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" t="s">
-        <v>35</v>
-      </c>
-      <c r="G128" t="s">
-        <v>498</v>
-      </c>
-      <c r="H128" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8">
-      <c r="B129" t="s">
-        <v>17</v>
-      </c>
-      <c r="C129" t="s">
-        <v>745</v>
-      </c>
-      <c r="D129" t="s">
-        <v>746</v>
-      </c>
-      <c r="E129" t="s">
-        <v>25</v>
-      </c>
-      <c r="F129" t="s">
-        <v>35</v>
-      </c>
-      <c r="G129" t="s">
-        <v>498</v>
-      </c>
-      <c r="H129" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="130" spans="2:8">
-      <c r="B130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C130" t="s">
-        <v>747</v>
-      </c>
-      <c r="D130" t="s">
-        <v>748</v>
-      </c>
-      <c r="E130" t="s">
-        <v>25</v>
-      </c>
-      <c r="F130" t="s">
-        <v>35</v>
-      </c>
-      <c r="G130" t="s">
-        <v>498</v>
-      </c>
-      <c r="H130" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="131" spans="2:8">
-      <c r="B131" t="s">
-        <v>17</v>
-      </c>
-      <c r="C131" t="s">
-        <v>749</v>
-      </c>
-      <c r="D131" t="s">
-        <v>750</v>
-      </c>
-      <c r="E131" t="s">
-        <v>25</v>
-      </c>
-      <c r="F131" t="s">
-        <v>35</v>
-      </c>
-      <c r="G131" t="s">
-        <v>498</v>
-      </c>
-      <c r="H131" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="132" spans="2:8">
-      <c r="B132" t="s">
-        <v>17</v>
-      </c>
-      <c r="C132" t="s">
-        <v>751</v>
-      </c>
-      <c r="D132" t="s">
-        <v>752</v>
-      </c>
-      <c r="E132" t="s">
-        <v>25</v>
-      </c>
-      <c r="F132" t="s">
-        <v>35</v>
-      </c>
-      <c r="G132" t="s">
-        <v>498</v>
-      </c>
-      <c r="H132" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="133" spans="2:8">
-      <c r="B133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C133" t="s">
-        <v>753</v>
-      </c>
-      <c r="D133" t="s">
-        <v>754</v>
-      </c>
-      <c r="E133" t="s">
-        <v>25</v>
-      </c>
-      <c r="F133" t="s">
-        <v>35</v>
-      </c>
-      <c r="G133" t="s">
-        <v>498</v>
-      </c>
-      <c r="H133" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="134" spans="2:8">
-      <c r="B134" t="s">
-        <v>17</v>
-      </c>
-      <c r="C134" t="s">
-        <v>755</v>
-      </c>
-      <c r="D134" t="s">
-        <v>756</v>
-      </c>
-      <c r="E134" t="s">
-        <v>25</v>
-      </c>
-      <c r="F134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G134" t="s">
-        <v>498</v>
-      </c>
-      <c r="H134" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="135" spans="2:8">
-      <c r="B135" t="s">
-        <v>17</v>
-      </c>
-      <c r="C135" t="s">
-        <v>757</v>
-      </c>
-      <c r="D135" t="s">
-        <v>758</v>
-      </c>
-      <c r="E135" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" t="s">
-        <v>35</v>
-      </c>
-      <c r="G135" t="s">
-        <v>498</v>
-      </c>
-      <c r="H135" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8">
-      <c r="B136" t="s">
-        <v>17</v>
-      </c>
-      <c r="C136" t="s">
-        <v>759</v>
-      </c>
-      <c r="D136" t="s">
-        <v>760</v>
-      </c>
-      <c r="E136" t="s">
-        <v>25</v>
-      </c>
-      <c r="F136" t="s">
-        <v>35</v>
-      </c>
-      <c r="G136" t="s">
-        <v>498</v>
-      </c>
-      <c r="H136" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8">
-      <c r="B137" t="s">
-        <v>17</v>
-      </c>
-      <c r="C137" t="s">
-        <v>761</v>
-      </c>
-      <c r="D137" t="s">
-        <v>762</v>
-      </c>
-      <c r="E137" t="s">
-        <v>25</v>
-      </c>
-      <c r="F137" t="s">
-        <v>35</v>
-      </c>
-      <c r="G137" t="s">
-        <v>498</v>
-      </c>
-      <c r="H137" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="138" spans="2:8">
-      <c r="B138" t="s">
-        <v>17</v>
-      </c>
-      <c r="C138" t="s">
-        <v>763</v>
-      </c>
-      <c r="D138" t="s">
-        <v>764</v>
-      </c>
-      <c r="E138" t="s">
-        <v>25</v>
-      </c>
-      <c r="F138" t="s">
-        <v>35</v>
-      </c>
-      <c r="G138" t="s">
-        <v>498</v>
-      </c>
-      <c r="H138" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="139" spans="2:8">
-      <c r="B139" t="s">
-        <v>17</v>
-      </c>
-      <c r="C139" t="s">
-        <v>765</v>
-      </c>
-      <c r="D139" t="s">
-        <v>766</v>
-      </c>
-      <c r="E139" t="s">
-        <v>25</v>
-      </c>
-      <c r="F139" t="s">
-        <v>35</v>
-      </c>
-      <c r="G139" t="s">
-        <v>498</v>
-      </c>
-      <c r="H139" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="140" spans="2:8">
-      <c r="B140" t="s">
-        <v>17</v>
-      </c>
-      <c r="C140" t="s">
-        <v>767</v>
-      </c>
-      <c r="D140" t="s">
-        <v>768</v>
-      </c>
-      <c r="E140" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" t="s">
-        <v>35</v>
-      </c>
-      <c r="G140" t="s">
-        <v>498</v>
-      </c>
-      <c r="H140" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="141" spans="2:8">
-      <c r="B141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C141" t="s">
-        <v>769</v>
-      </c>
-      <c r="D141" t="s">
-        <v>770</v>
-      </c>
-      <c r="E141" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" t="s">
-        <v>35</v>
-      </c>
-      <c r="G141" t="s">
-        <v>498</v>
-      </c>
-      <c r="H141" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="142" spans="2:8">
-      <c r="B142" t="s">
-        <v>17</v>
-      </c>
-      <c r="C142" t="s">
-        <v>771</v>
-      </c>
-      <c r="D142" t="s">
-        <v>772</v>
-      </c>
-      <c r="E142" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" t="s">
-        <v>35</v>
-      </c>
-      <c r="G142" t="s">
-        <v>498</v>
-      </c>
-      <c r="H142" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="143" spans="2:8">
-      <c r="B143" t="s">
-        <v>17</v>
-      </c>
-      <c r="C143" t="s">
-        <v>773</v>
-      </c>
-      <c r="D143" t="s">
-        <v>774</v>
-      </c>
-      <c r="E143" t="s">
-        <v>25</v>
-      </c>
-      <c r="F143" t="s">
-        <v>35</v>
-      </c>
-      <c r="G143" t="s">
-        <v>498</v>
-      </c>
-      <c r="H143" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="144" spans="2:8">
-      <c r="B144" t="s">
-        <v>17</v>
-      </c>
-      <c r="C144" t="s">
-        <v>775</v>
-      </c>
-      <c r="D144" t="s">
-        <v>776</v>
-      </c>
-      <c r="E144" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" t="s">
-        <v>35</v>
-      </c>
-      <c r="G144" t="s">
-        <v>498</v>
-      </c>
-      <c r="H144" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="145" spans="2:8">
-      <c r="B145" t="s">
-        <v>17</v>
-      </c>
-      <c r="C145" t="s">
-        <v>777</v>
-      </c>
-      <c r="D145" t="s">
-        <v>778</v>
-      </c>
-      <c r="E145" t="s">
-        <v>25</v>
-      </c>
-      <c r="F145" t="s">
-        <v>35</v>
-      </c>
-      <c r="G145" t="s">
-        <v>498</v>
-      </c>
-      <c r="H145" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="146" spans="2:8">
-      <c r="B146" t="s">
-        <v>17</v>
-      </c>
-      <c r="C146" t="s">
-        <v>779</v>
-      </c>
-      <c r="D146" t="s">
-        <v>780</v>
-      </c>
-      <c r="E146" t="s">
-        <v>25</v>
-      </c>
-      <c r="F146" t="s">
-        <v>35</v>
-      </c>
-      <c r="G146" t="s">
-        <v>498</v>
-      </c>
-      <c r="H146" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="147" spans="2:8">
-      <c r="B147" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" t="s">
-        <v>781</v>
-      </c>
-      <c r="D147" t="s">
-        <v>782</v>
-      </c>
-      <c r="E147" t="s">
-        <v>25</v>
-      </c>
-      <c r="F147" t="s">
-        <v>35</v>
-      </c>
-      <c r="G147" t="s">
-        <v>498</v>
-      </c>
-      <c r="H147" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="148" spans="2:8">
-      <c r="B148" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" t="s">
-        <v>783</v>
-      </c>
-      <c r="D148" t="s">
-        <v>784</v>
-      </c>
-      <c r="E148" t="s">
-        <v>25</v>
-      </c>
-      <c r="F148" t="s">
-        <v>35</v>
-      </c>
-      <c r="G148" t="s">
-        <v>498</v>
-      </c>
-      <c r="H148" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="149" spans="2:8">
-      <c r="B149" t="s">
-        <v>17</v>
-      </c>
-      <c r="C149" t="s">
-        <v>785</v>
-      </c>
-      <c r="D149" t="s">
-        <v>786</v>
-      </c>
-      <c r="E149" t="s">
-        <v>25</v>
-      </c>
-      <c r="F149" t="s">
-        <v>35</v>
-      </c>
-      <c r="G149" t="s">
-        <v>498</v>
-      </c>
-      <c r="H149" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8">
-      <c r="B150" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" t="s">
-        <v>787</v>
-      </c>
-      <c r="D150" t="s">
-        <v>788</v>
-      </c>
-      <c r="E150" t="s">
-        <v>25</v>
-      </c>
-      <c r="F150" t="s">
-        <v>35</v>
-      </c>
-      <c r="G150" t="s">
-        <v>498</v>
-      </c>
-      <c r="H150" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="151" spans="2:8">
-      <c r="B151" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" t="s">
-        <v>789</v>
-      </c>
-      <c r="D151" t="s">
-        <v>790</v>
-      </c>
-      <c r="E151" t="s">
-        <v>25</v>
-      </c>
-      <c r="F151" t="s">
-        <v>35</v>
-      </c>
-      <c r="G151" t="s">
-        <v>498</v>
-      </c>
-      <c r="H151" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="152" spans="2:8">
-      <c r="B152" t="s">
-        <v>17</v>
-      </c>
-      <c r="C152" t="s">
-        <v>791</v>
-      </c>
-      <c r="D152" t="s">
-        <v>792</v>
-      </c>
-      <c r="E152" t="s">
-        <v>25</v>
-      </c>
-      <c r="F152" t="s">
-        <v>35</v>
-      </c>
-      <c r="G152" t="s">
-        <v>498</v>
-      </c>
-      <c r="H152" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="153" spans="2:8">
-      <c r="B153" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" t="s">
-        <v>793</v>
-      </c>
-      <c r="D153" t="s">
-        <v>794</v>
-      </c>
-      <c r="E153" t="s">
-        <v>25</v>
-      </c>
-      <c r="F153" t="s">
-        <v>35</v>
-      </c>
-      <c r="G153" t="s">
-        <v>498</v>
-      </c>
-      <c r="H153" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="154" spans="2:8">
-      <c r="B154" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" t="s">
-        <v>795</v>
-      </c>
-      <c r="D154" t="s">
-        <v>796</v>
-      </c>
-      <c r="E154" t="s">
-        <v>25</v>
-      </c>
-      <c r="F154" t="s">
-        <v>35</v>
-      </c>
-      <c r="G154" t="s">
-        <v>498</v>
-      </c>
-      <c r="H154" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="155" spans="2:8">
-      <c r="B155" t="s">
-        <v>17</v>
-      </c>
-      <c r="C155" t="s">
-        <v>797</v>
-      </c>
-      <c r="D155" t="s">
-        <v>798</v>
-      </c>
-      <c r="E155" t="s">
-        <v>25</v>
-      </c>
-      <c r="F155" t="s">
-        <v>35</v>
-      </c>
-      <c r="G155" t="s">
-        <v>498</v>
-      </c>
-      <c r="H155" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="156" spans="2:8">
-      <c r="B156" t="s">
-        <v>17</v>
-      </c>
-      <c r="C156" t="s">
-        <v>799</v>
-      </c>
-      <c r="D156" t="s">
-        <v>800</v>
-      </c>
-      <c r="E156" t="s">
-        <v>25</v>
-      </c>
-      <c r="F156" t="s">
-        <v>35</v>
-      </c>
-      <c r="G156" t="s">
-        <v>498</v>
-      </c>
-      <c r="H156" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="157" spans="2:8">
-      <c r="B157" t="s">
-        <v>17</v>
-      </c>
-      <c r="C157" t="s">
-        <v>801</v>
-      </c>
-      <c r="D157" t="s">
-        <v>802</v>
-      </c>
-      <c r="E157" t="s">
-        <v>25</v>
-      </c>
-      <c r="F157" t="s">
-        <v>35</v>
-      </c>
-      <c r="G157" t="s">
-        <v>498</v>
-      </c>
-      <c r="H157" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="158" spans="2:8">
-      <c r="B158" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" t="s">
-        <v>803</v>
-      </c>
-      <c r="D158" t="s">
-        <v>804</v>
-      </c>
-      <c r="E158" t="s">
-        <v>25</v>
-      </c>
-      <c r="F158" t="s">
-        <v>35</v>
-      </c>
-      <c r="G158" t="s">
-        <v>498</v>
-      </c>
-      <c r="H158" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="159" spans="2:8">
-      <c r="B159" t="s">
-        <v>17</v>
-      </c>
-      <c r="C159" t="s">
-        <v>805</v>
-      </c>
-      <c r="D159" t="s">
-        <v>806</v>
-      </c>
-      <c r="E159" t="s">
-        <v>25</v>
-      </c>
-      <c r="F159" t="s">
-        <v>35</v>
-      </c>
-      <c r="G159" t="s">
-        <v>498</v>
-      </c>
-      <c r="H159" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="160" spans="2:8">
-      <c r="B160" t="s">
-        <v>17</v>
-      </c>
-      <c r="C160" t="s">
-        <v>807</v>
-      </c>
-      <c r="D160" t="s">
-        <v>808</v>
-      </c>
-      <c r="E160" t="s">
-        <v>25</v>
-      </c>
-      <c r="F160" t="s">
-        <v>35</v>
-      </c>
-      <c r="G160" t="s">
-        <v>498</v>
-      </c>
-      <c r="H160" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="161" spans="2:8">
-      <c r="B161" t="s">
-        <v>17</v>
-      </c>
-      <c r="C161" t="s">
-        <v>809</v>
-      </c>
-      <c r="D161" t="s">
-        <v>810</v>
-      </c>
-      <c r="E161" t="s">
-        <v>25</v>
-      </c>
-      <c r="F161" t="s">
-        <v>35</v>
-      </c>
-      <c r="G161" t="s">
-        <v>498</v>
-      </c>
-      <c r="H161" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="162" spans="2:8">
-      <c r="B162" t="s">
-        <v>17</v>
-      </c>
-      <c r="C162" t="s">
-        <v>811</v>
-      </c>
-      <c r="D162" t="s">
-        <v>812</v>
-      </c>
-      <c r="E162" t="s">
-        <v>25</v>
-      </c>
-      <c r="F162" t="s">
-        <v>35</v>
-      </c>
-      <c r="G162" t="s">
-        <v>498</v>
-      </c>
-      <c r="H162" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="163" spans="2:8">
-      <c r="B163" t="s">
-        <v>17</v>
-      </c>
-      <c r="C163" t="s">
-        <v>813</v>
-      </c>
-      <c r="D163" t="s">
-        <v>814</v>
-      </c>
-      <c r="E163" t="s">
-        <v>25</v>
-      </c>
-      <c r="F163" t="s">
-        <v>35</v>
-      </c>
-      <c r="G163" t="s">
-        <v>498</v>
-      </c>
-      <c r="H163" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8">
-      <c r="B164" t="s">
-        <v>17</v>
-      </c>
-      <c r="C164" t="s">
-        <v>815</v>
-      </c>
-      <c r="D164" t="s">
-        <v>816</v>
-      </c>
-      <c r="E164" t="s">
-        <v>25</v>
-      </c>
-      <c r="F164" t="s">
-        <v>35</v>
-      </c>
-      <c r="G164" t="s">
-        <v>498</v>
-      </c>
-      <c r="H164" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="165" spans="2:8">
-      <c r="B165" t="s">
-        <v>17</v>
-      </c>
-      <c r="C165" t="s">
-        <v>817</v>
-      </c>
-      <c r="D165" t="s">
-        <v>818</v>
-      </c>
-      <c r="E165" t="s">
-        <v>25</v>
-      </c>
-      <c r="F165" t="s">
-        <v>35</v>
-      </c>
-      <c r="G165" t="s">
-        <v>498</v>
-      </c>
-      <c r="H165" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8">
-      <c r="B166" t="s">
-        <v>17</v>
-      </c>
-      <c r="C166" t="s">
-        <v>819</v>
-      </c>
-      <c r="D166" t="s">
-        <v>820</v>
-      </c>
-      <c r="E166" t="s">
-        <v>25</v>
-      </c>
-      <c r="F166" t="s">
-        <v>35</v>
-      </c>
-      <c r="G166" t="s">
-        <v>498</v>
-      </c>
-      <c r="H166" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="167" spans="2:8">
-      <c r="B167" t="s">
-        <v>17</v>
-      </c>
-      <c r="C167" t="s">
-        <v>821</v>
-      </c>
-      <c r="D167" t="s">
-        <v>822</v>
-      </c>
-      <c r="E167" t="s">
-        <v>25</v>
-      </c>
-      <c r="F167" t="s">
-        <v>35</v>
-      </c>
-      <c r="G167" t="s">
-        <v>498</v>
-      </c>
-      <c r="H167" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="168" spans="2:8">
-      <c r="B168" t="s">
-        <v>17</v>
-      </c>
-      <c r="C168" t="s">
-        <v>823</v>
-      </c>
-      <c r="D168" t="s">
-        <v>824</v>
-      </c>
-      <c r="E168" t="s">
-        <v>25</v>
-      </c>
-      <c r="F168" t="s">
-        <v>35</v>
-      </c>
-      <c r="G168" t="s">
-        <v>498</v>
-      </c>
-      <c r="H168" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="169" spans="2:8">
-      <c r="B169" t="s">
-        <v>17</v>
-      </c>
-      <c r="C169" t="s">
-        <v>825</v>
-      </c>
-      <c r="D169" t="s">
-        <v>826</v>
-      </c>
-      <c r="E169" t="s">
-        <v>25</v>
-      </c>
-      <c r="F169" t="s">
-        <v>35</v>
-      </c>
-      <c r="G169" t="s">
-        <v>498</v>
-      </c>
-      <c r="H169" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="170" spans="2:8">
-      <c r="B170" t="s">
-        <v>17</v>
-      </c>
-      <c r="C170" t="s">
-        <v>827</v>
-      </c>
-      <c r="D170" t="s">
-        <v>828</v>
-      </c>
-      <c r="E170" t="s">
-        <v>25</v>
-      </c>
-      <c r="F170" t="s">
-        <v>35</v>
-      </c>
-      <c r="G170" t="s">
-        <v>498</v>
-      </c>
-      <c r="H170" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="171" spans="2:8">
-      <c r="B171" t="s">
-        <v>17</v>
-      </c>
-      <c r="C171" t="s">
-        <v>829</v>
-      </c>
-      <c r="D171" t="s">
-        <v>830</v>
-      </c>
-      <c r="E171" t="s">
-        <v>25</v>
-      </c>
-      <c r="F171" t="s">
-        <v>35</v>
-      </c>
-      <c r="G171" t="s">
-        <v>498</v>
-      </c>
-      <c r="H171" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="172" spans="2:8">
-      <c r="B172" t="s">
-        <v>17</v>
-      </c>
-      <c r="C172" t="s">
-        <v>831</v>
-      </c>
-      <c r="D172" t="s">
-        <v>832</v>
-      </c>
-      <c r="E172" t="s">
-        <v>25</v>
-      </c>
-      <c r="F172" t="s">
-        <v>35</v>
-      </c>
-      <c r="G172" t="s">
-        <v>498</v>
-      </c>
-      <c r="H172" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="173" spans="2:8">
-      <c r="B173" t="s">
-        <v>17</v>
-      </c>
-      <c r="C173" t="s">
-        <v>833</v>
-      </c>
-      <c r="D173" t="s">
-        <v>834</v>
-      </c>
-      <c r="E173" t="s">
-        <v>25</v>
-      </c>
-      <c r="F173" t="s">
-        <v>35</v>
-      </c>
-      <c r="G173" t="s">
-        <v>498</v>
-      </c>
-      <c r="H173" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="174" spans="2:8">
-      <c r="B174" t="s">
-        <v>17</v>
-      </c>
-      <c r="C174" t="s">
-        <v>835</v>
-      </c>
-      <c r="D174" t="s">
-        <v>836</v>
-      </c>
-      <c r="E174" t="s">
-        <v>25</v>
-      </c>
-      <c r="F174" t="s">
-        <v>35</v>
-      </c>
-      <c r="G174" t="s">
-        <v>498</v>
-      </c>
-      <c r="H174" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="175" spans="2:8">
-      <c r="B175" t="s">
-        <v>17</v>
-      </c>
-      <c r="C175" t="s">
-        <v>837</v>
-      </c>
-      <c r="D175" t="s">
-        <v>838</v>
-      </c>
-      <c r="E175" t="s">
-        <v>25</v>
-      </c>
-      <c r="F175" t="s">
-        <v>35</v>
-      </c>
-      <c r="G175" t="s">
-        <v>498</v>
-      </c>
-      <c r="H175" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="176" spans="2:8">
-      <c r="B176" t="s">
-        <v>17</v>
-      </c>
-      <c r="C176" t="s">
-        <v>839</v>
-      </c>
-      <c r="D176" t="s">
-        <v>840</v>
-      </c>
-      <c r="E176" t="s">
-        <v>25</v>
-      </c>
-      <c r="F176" t="s">
-        <v>35</v>
-      </c>
-      <c r="G176" t="s">
-        <v>498</v>
-      </c>
-      <c r="H176" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="177" spans="2:8">
-      <c r="B177" t="s">
-        <v>17</v>
-      </c>
-      <c r="C177" t="s">
-        <v>841</v>
-      </c>
-      <c r="D177" t="s">
-        <v>842</v>
-      </c>
-      <c r="E177" t="s">
-        <v>25</v>
-      </c>
-      <c r="F177" t="s">
-        <v>35</v>
-      </c>
-      <c r="G177" t="s">
-        <v>498</v>
-      </c>
-      <c r="H177" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="178" spans="2:8">
-      <c r="B178" t="s">
-        <v>17</v>
-      </c>
-      <c r="C178" t="s">
-        <v>843</v>
-      </c>
-      <c r="D178" t="s">
-        <v>844</v>
-      </c>
-      <c r="E178" t="s">
-        <v>25</v>
-      </c>
-      <c r="F178" t="s">
-        <v>35</v>
-      </c>
-      <c r="G178" t="s">
-        <v>498</v>
-      </c>
-      <c r="H178" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="179" spans="2:8">
-      <c r="B179" t="s">
-        <v>17</v>
-      </c>
-      <c r="C179" t="s">
-        <v>845</v>
-      </c>
-      <c r="D179" t="s">
-        <v>846</v>
-      </c>
-      <c r="E179" t="s">
-        <v>25</v>
-      </c>
-      <c r="F179" t="s">
-        <v>35</v>
-      </c>
-      <c r="G179" t="s">
-        <v>498</v>
-      </c>
-      <c r="H179" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="180" spans="2:8">
-      <c r="B180" t="s">
-        <v>17</v>
-      </c>
-      <c r="C180" t="s">
-        <v>847</v>
-      </c>
-      <c r="D180" t="s">
-        <v>848</v>
-      </c>
-      <c r="E180" t="s">
-        <v>25</v>
-      </c>
-      <c r="F180" t="s">
-        <v>35</v>
-      </c>
-      <c r="G180" t="s">
-        <v>498</v>
-      </c>
-      <c r="H180" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="181" spans="2:8">
-      <c r="B181" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" t="s">
-        <v>849</v>
-      </c>
-      <c r="D181" t="s">
-        <v>850</v>
-      </c>
-      <c r="E181" t="s">
-        <v>25</v>
-      </c>
-      <c r="F181" t="s">
-        <v>35</v>
-      </c>
-      <c r="G181" t="s">
-        <v>498</v>
-      </c>
-      <c r="H181" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="182" spans="2:8">
-      <c r="B182" t="s">
-        <v>17</v>
-      </c>
-      <c r="C182" t="s">
-        <v>851</v>
-      </c>
-      <c r="D182" t="s">
-        <v>852</v>
-      </c>
-      <c r="E182" t="s">
-        <v>25</v>
-      </c>
-      <c r="F182" t="s">
-        <v>35</v>
-      </c>
-      <c r="G182" t="s">
-        <v>498</v>
-      </c>
-      <c r="H182" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="183" spans="2:8">
-      <c r="B183" t="s">
-        <v>17</v>
-      </c>
-      <c r="C183" t="s">
-        <v>853</v>
-      </c>
-      <c r="D183" t="s">
-        <v>854</v>
-      </c>
-      <c r="E183" t="s">
-        <v>25</v>
-      </c>
-      <c r="F183" t="s">
-        <v>35</v>
-      </c>
-      <c r="G183" t="s">
-        <v>498</v>
-      </c>
-      <c r="H183" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="184" spans="2:8">
-      <c r="B184" t="s">
-        <v>17</v>
-      </c>
-      <c r="C184" t="s">
-        <v>855</v>
-      </c>
-      <c r="D184" t="s">
-        <v>856</v>
-      </c>
-      <c r="E184" t="s">
-        <v>25</v>
-      </c>
-      <c r="F184" t="s">
-        <v>35</v>
-      </c>
-      <c r="G184" t="s">
-        <v>498</v>
-      </c>
-      <c r="H184" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="185" spans="2:8">
-      <c r="B185" t="s">
-        <v>17</v>
-      </c>
-      <c r="C185" t="s">
-        <v>857</v>
-      </c>
-      <c r="D185" t="s">
-        <v>858</v>
-      </c>
-      <c r="E185" t="s">
-        <v>25</v>
-      </c>
-      <c r="F185" t="s">
-        <v>35</v>
-      </c>
-      <c r="G185" t="s">
-        <v>498</v>
-      </c>
-      <c r="H185" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="186" spans="2:8">
-      <c r="B186" t="s">
-        <v>17</v>
-      </c>
-      <c r="C186" t="s">
-        <v>859</v>
-      </c>
-      <c r="D186" t="s">
-        <v>860</v>
-      </c>
-      <c r="E186" t="s">
-        <v>25</v>
-      </c>
-      <c r="F186" t="s">
-        <v>35</v>
-      </c>
-      <c r="G186" t="s">
-        <v>498</v>
-      </c>
-      <c r="H186" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="187" spans="2:8">
-      <c r="B187" t="s">
-        <v>17</v>
-      </c>
-      <c r="C187" t="s">
-        <v>861</v>
-      </c>
-      <c r="D187" t="s">
-        <v>862</v>
-      </c>
-      <c r="E187" t="s">
-        <v>25</v>
-      </c>
-      <c r="F187" t="s">
-        <v>35</v>
-      </c>
-      <c r="G187" t="s">
-        <v>498</v>
-      </c>
-      <c r="H187" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="188" spans="2:8">
-      <c r="B188" t="s">
-        <v>17</v>
-      </c>
-      <c r="C188" t="s">
-        <v>863</v>
-      </c>
-      <c r="D188" t="s">
-        <v>864</v>
-      </c>
-      <c r="E188" t="s">
-        <v>25</v>
-      </c>
-      <c r="F188" t="s">
-        <v>35</v>
-      </c>
-      <c r="G188" t="s">
-        <v>498</v>
-      </c>
-      <c r="H188" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="189" spans="2:8">
-      <c r="B189" t="s">
-        <v>17</v>
-      </c>
-      <c r="C189" t="s">
-        <v>865</v>
-      </c>
-      <c r="D189" t="s">
-        <v>866</v>
-      </c>
-      <c r="E189" t="s">
-        <v>25</v>
-      </c>
-      <c r="F189" t="s">
-        <v>35</v>
-      </c>
-      <c r="G189" t="s">
-        <v>498</v>
-      </c>
-      <c r="H189" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="190" spans="2:8">
-      <c r="B190" t="s">
-        <v>17</v>
-      </c>
-      <c r="C190" t="s">
-        <v>867</v>
-      </c>
-      <c r="D190" t="s">
-        <v>868</v>
-      </c>
-      <c r="E190" t="s">
-        <v>25</v>
-      </c>
-      <c r="F190" t="s">
-        <v>35</v>
-      </c>
-      <c r="G190" t="s">
-        <v>498</v>
-      </c>
-      <c r="H190" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="191" spans="2:8">
-      <c r="B191" t="s">
-        <v>17</v>
-      </c>
-      <c r="C191" t="s">
-        <v>869</v>
-      </c>
-      <c r="D191" t="s">
-        <v>870</v>
-      </c>
-      <c r="E191" t="s">
-        <v>25</v>
-      </c>
-      <c r="F191" t="s">
-        <v>35</v>
-      </c>
-      <c r="G191" t="s">
-        <v>498</v>
-      </c>
-      <c r="H191" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="192" spans="2:8">
-      <c r="B192" t="s">
-        <v>17</v>
-      </c>
-      <c r="C192" t="s">
-        <v>871</v>
-      </c>
-      <c r="D192" t="s">
-        <v>872</v>
-      </c>
-      <c r="E192" t="s">
-        <v>25</v>
-      </c>
-      <c r="F192" t="s">
-        <v>35</v>
-      </c>
-      <c r="G192" t="s">
-        <v>498</v>
-      </c>
-      <c r="H192" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="193" spans="2:8">
-      <c r="B193" t="s">
-        <v>17</v>
-      </c>
-      <c r="C193" t="s">
-        <v>873</v>
-      </c>
-      <c r="D193" t="s">
-        <v>874</v>
-      </c>
-      <c r="E193" t="s">
-        <v>25</v>
-      </c>
-      <c r="F193" t="s">
-        <v>35</v>
-      </c>
-      <c r="G193" t="s">
-        <v>498</v>
-      </c>
-      <c r="H193" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="194" spans="2:8">
-      <c r="B194" t="s">
-        <v>17</v>
-      </c>
-      <c r="C194" t="s">
-        <v>875</v>
-      </c>
-      <c r="D194" t="s">
-        <v>876</v>
-      </c>
-      <c r="E194" t="s">
-        <v>25</v>
-      </c>
-      <c r="F194" t="s">
-        <v>35</v>
-      </c>
-      <c r="G194" t="s">
-        <v>498</v>
-      </c>
-      <c r="H194" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="195" spans="2:8">
-      <c r="B195" t="s">
-        <v>17</v>
-      </c>
-      <c r="C195" t="s">
-        <v>877</v>
-      </c>
-      <c r="D195" t="s">
-        <v>878</v>
-      </c>
-      <c r="E195" t="s">
-        <v>25</v>
-      </c>
-      <c r="F195" t="s">
-        <v>35</v>
-      </c>
-      <c r="G195" t="s">
-        <v>498</v>
-      </c>
-      <c r="H195" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="196" spans="2:8">
-      <c r="B196" t="s">
-        <v>17</v>
-      </c>
-      <c r="C196" t="s">
-        <v>879</v>
-      </c>
-      <c r="D196" t="s">
-        <v>880</v>
-      </c>
-      <c r="E196" t="s">
-        <v>25</v>
-      </c>
-      <c r="F196" t="s">
-        <v>35</v>
-      </c>
-      <c r="G196" t="s">
-        <v>498</v>
-      </c>
-      <c r="H196" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="197" spans="2:8">
-      <c r="B197" t="s">
-        <v>17</v>
-      </c>
-      <c r="C197" t="s">
-        <v>881</v>
-      </c>
-      <c r="D197" t="s">
-        <v>882</v>
-      </c>
-      <c r="E197" t="s">
-        <v>25</v>
-      </c>
-      <c r="F197" t="s">
-        <v>35</v>
-      </c>
-      <c r="G197" t="s">
-        <v>498</v>
-      </c>
-      <c r="H197" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="198" spans="2:8">
-      <c r="B198" t="s">
-        <v>17</v>
-      </c>
-      <c r="C198" t="s">
-        <v>883</v>
-      </c>
-      <c r="D198" t="s">
-        <v>884</v>
-      </c>
-      <c r="E198" t="s">
-        <v>25</v>
-      </c>
-      <c r="F198" t="s">
-        <v>35</v>
-      </c>
-      <c r="G198" t="s">
-        <v>498</v>
-      </c>
-      <c r="H198" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="199" spans="2:8">
-      <c r="B199" t="s">
-        <v>17</v>
-      </c>
-      <c r="C199" t="s">
-        <v>885</v>
-      </c>
-      <c r="D199" t="s">
-        <v>886</v>
-      </c>
-      <c r="E199" t="s">
-        <v>25</v>
-      </c>
-      <c r="F199" t="s">
-        <v>35</v>
-      </c>
-      <c r="G199" t="s">
-        <v>498</v>
-      </c>
-      <c r="H199" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="200" spans="2:8">
-      <c r="B200" t="s">
-        <v>17</v>
-      </c>
-      <c r="C200" t="s">
-        <v>887</v>
-      </c>
-      <c r="D200" t="s">
-        <v>888</v>
-      </c>
-      <c r="E200" t="s">
-        <v>25</v>
-      </c>
-      <c r="F200" t="s">
-        <v>35</v>
-      </c>
-      <c r="G200" t="s">
-        <v>498</v>
-      </c>
-      <c r="H200" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="201" spans="2:8">
-      <c r="B201" t="s">
-        <v>17</v>
-      </c>
-      <c r="C201" t="s">
-        <v>889</v>
-      </c>
-      <c r="D201" t="s">
-        <v>890</v>
-      </c>
-      <c r="E201" t="s">
-        <v>25</v>
-      </c>
-      <c r="F201" t="s">
-        <v>35</v>
-      </c>
-      <c r="G201" t="s">
-        <v>498</v>
-      </c>
-      <c r="H201" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="202" spans="2:8">
-      <c r="B202" t="s">
-        <v>17</v>
-      </c>
-      <c r="C202" t="s">
-        <v>891</v>
-      </c>
-      <c r="D202" t="s">
-        <v>892</v>
-      </c>
-      <c r="E202" t="s">
-        <v>25</v>
-      </c>
-      <c r="F202" t="s">
-        <v>35</v>
-      </c>
-      <c r="G202" t="s">
-        <v>498</v>
-      </c>
-      <c r="H202" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="203" spans="2:8">
-      <c r="B203" t="s">
-        <v>17</v>
-      </c>
-      <c r="C203" t="s">
-        <v>893</v>
-      </c>
-      <c r="D203" t="s">
-        <v>894</v>
-      </c>
-      <c r="E203" t="s">
-        <v>25</v>
-      </c>
-      <c r="F203" t="s">
-        <v>35</v>
-      </c>
-      <c r="G203" t="s">
-        <v>498</v>
-      </c>
-      <c r="H203" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="204" spans="2:8">
-      <c r="B204" t="s">
-        <v>17</v>
-      </c>
-      <c r="C204" t="s">
-        <v>895</v>
-      </c>
-      <c r="D204" t="s">
-        <v>896</v>
-      </c>
-      <c r="E204" t="s">
-        <v>25</v>
-      </c>
-      <c r="F204" t="s">
-        <v>35</v>
-      </c>
-      <c r="G204" t="s">
-        <v>498</v>
-      </c>
-      <c r="H204" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="205" spans="2:8">
-      <c r="B205" t="s">
-        <v>17</v>
-      </c>
-      <c r="C205" t="s">
-        <v>897</v>
-      </c>
-      <c r="D205" t="s">
-        <v>898</v>
-      </c>
-      <c r="E205" t="s">
-        <v>25</v>
-      </c>
-      <c r="F205" t="s">
-        <v>35</v>
-      </c>
-      <c r="G205" t="s">
-        <v>498</v>
-      </c>
-      <c r="H205" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="206" spans="2:8">
-      <c r="B206" t="s">
-        <v>17</v>
-      </c>
-      <c r="C206" t="s">
-        <v>899</v>
-      </c>
-      <c r="D206" t="s">
-        <v>900</v>
-      </c>
-      <c r="E206" t="s">
-        <v>25</v>
-      </c>
-      <c r="F206" t="s">
-        <v>35</v>
-      </c>
-      <c r="G206" t="s">
-        <v>498</v>
-      </c>
-      <c r="H206" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="207" spans="2:8">
-      <c r="B207" t="s">
-        <v>17</v>
-      </c>
-      <c r="C207" t="s">
-        <v>901</v>
-      </c>
-      <c r="D207" t="s">
-        <v>902</v>
-      </c>
-      <c r="E207" t="s">
-        <v>25</v>
-      </c>
-      <c r="F207" t="s">
-        <v>35</v>
-      </c>
-      <c r="G207" t="s">
-        <v>498</v>
-      </c>
-      <c r="H207" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="208" spans="2:8">
-      <c r="B208" t="s">
-        <v>17</v>
-      </c>
-      <c r="C208" t="s">
-        <v>903</v>
-      </c>
-      <c r="D208" t="s">
-        <v>904</v>
-      </c>
-      <c r="E208" t="s">
-        <v>25</v>
-      </c>
-      <c r="F208" t="s">
-        <v>35</v>
-      </c>
-      <c r="G208" t="s">
-        <v>498</v>
-      </c>
-      <c r="H208" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="209" spans="2:8">
-      <c r="B209" t="s">
-        <v>17</v>
-      </c>
-      <c r="C209" t="s">
-        <v>905</v>
-      </c>
-      <c r="D209" t="s">
-        <v>906</v>
-      </c>
-      <c r="E209" t="s">
-        <v>25</v>
-      </c>
-      <c r="F209" t="s">
-        <v>35</v>
-      </c>
-      <c r="G209" t="s">
-        <v>498</v>
-      </c>
-      <c r="H209" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="210" spans="2:8">
-      <c r="B210" t="s">
-        <v>17</v>
-      </c>
-      <c r="C210" t="s">
-        <v>907</v>
-      </c>
-      <c r="D210" t="s">
-        <v>908</v>
-      </c>
-      <c r="E210" t="s">
-        <v>25</v>
-      </c>
-      <c r="F210" t="s">
-        <v>35</v>
-      </c>
-      <c r="G210" t="s">
-        <v>498</v>
-      </c>
-      <c r="H210" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="211" spans="2:8">
-      <c r="B211" t="s">
-        <v>17</v>
-      </c>
-      <c r="C211" t="s">
-        <v>909</v>
-      </c>
-      <c r="D211" t="s">
-        <v>910</v>
-      </c>
-      <c r="E211" t="s">
-        <v>25</v>
-      </c>
-      <c r="F211" t="s">
-        <v>35</v>
-      </c>
-      <c r="G211" t="s">
-        <v>498</v>
-      </c>
-      <c r="H211" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="212" spans="2:8">
-      <c r="B212" t="s">
-        <v>17</v>
-      </c>
-      <c r="C212" t="s">
-        <v>911</v>
-      </c>
-      <c r="D212" t="s">
-        <v>912</v>
-      </c>
-      <c r="E212" t="s">
-        <v>25</v>
-      </c>
-      <c r="F212" t="s">
-        <v>35</v>
-      </c>
-      <c r="G212" t="s">
-        <v>498</v>
-      </c>
-      <c r="H212" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="213" spans="2:8">
-      <c r="B213" t="s">
-        <v>17</v>
-      </c>
-      <c r="C213" t="s">
-        <v>913</v>
-      </c>
-      <c r="D213" t="s">
-        <v>914</v>
-      </c>
-      <c r="E213" t="s">
-        <v>25</v>
-      </c>
-      <c r="F213" t="s">
-        <v>35</v>
-      </c>
-      <c r="G213" t="s">
-        <v>498</v>
-      </c>
-      <c r="H213" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="214" spans="2:8">
-      <c r="B214" t="s">
-        <v>17</v>
-      </c>
-      <c r="C214" t="s">
-        <v>915</v>
-      </c>
-      <c r="D214" t="s">
-        <v>916</v>
-      </c>
-      <c r="E214" t="s">
-        <v>25</v>
-      </c>
-      <c r="F214" t="s">
-        <v>35</v>
-      </c>
-      <c r="G214" t="s">
-        <v>498</v>
-      </c>
-      <c r="H214" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="215" spans="2:8">
-      <c r="B215" t="s">
-        <v>17</v>
-      </c>
-      <c r="C215" t="s">
-        <v>917</v>
-      </c>
-      <c r="D215" t="s">
-        <v>918</v>
-      </c>
-      <c r="E215" t="s">
-        <v>25</v>
-      </c>
-      <c r="F215" t="s">
-        <v>35</v>
-      </c>
-      <c r="G215" t="s">
-        <v>498</v>
-      </c>
-      <c r="H215" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="216" spans="2:8">
-      <c r="B216" t="s">
-        <v>17</v>
-      </c>
-      <c r="C216" t="s">
-        <v>919</v>
-      </c>
-      <c r="D216" t="s">
-        <v>920</v>
-      </c>
-      <c r="E216" t="s">
-        <v>25</v>
-      </c>
-      <c r="F216" t="s">
-        <v>35</v>
-      </c>
-      <c r="G216" t="s">
-        <v>498</v>
-      </c>
-      <c r="H216" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="217" spans="2:8">
-      <c r="B217" t="s">
-        <v>17</v>
-      </c>
-      <c r="C217" t="s">
-        <v>921</v>
-      </c>
-      <c r="D217" t="s">
-        <v>922</v>
-      </c>
-      <c r="E217" t="s">
-        <v>25</v>
-      </c>
-      <c r="F217" t="s">
-        <v>35</v>
-      </c>
-      <c r="G217" t="s">
-        <v>498</v>
-      </c>
-      <c r="H217" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="218" spans="2:8">
-      <c r="B218" t="s">
-        <v>17</v>
-      </c>
-      <c r="C218" t="s">
-        <v>923</v>
-      </c>
-      <c r="D218" t="s">
-        <v>924</v>
-      </c>
-      <c r="E218" t="s">
-        <v>25</v>
-      </c>
-      <c r="F218" t="s">
-        <v>35</v>
-      </c>
-      <c r="G218" t="s">
-        <v>498</v>
-      </c>
-      <c r="H218" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="219" spans="2:8">
-      <c r="B219" t="s">
-        <v>17</v>
-      </c>
-      <c r="C219" t="s">
-        <v>925</v>
-      </c>
-      <c r="D219" t="s">
-        <v>926</v>
-      </c>
-      <c r="E219" t="s">
-        <v>25</v>
-      </c>
-      <c r="F219" t="s">
-        <v>35</v>
-      </c>
-      <c r="G219" t="s">
-        <v>498</v>
-      </c>
-      <c r="H219" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="220" spans="2:8">
-      <c r="B220" t="s">
-        <v>17</v>
-      </c>
-      <c r="C220" t="s">
-        <v>927</v>
-      </c>
-      <c r="D220" t="s">
-        <v>928</v>
-      </c>
-      <c r="E220" t="s">
-        <v>25</v>
-      </c>
-      <c r="F220" t="s">
-        <v>35</v>
-      </c>
-      <c r="G220" t="s">
-        <v>498</v>
-      </c>
-      <c r="H220" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="221" spans="2:8">
-      <c r="B221" t="s">
-        <v>17</v>
-      </c>
-      <c r="C221" t="s">
-        <v>929</v>
-      </c>
-      <c r="D221" t="s">
-        <v>930</v>
-      </c>
-      <c r="E221" t="s">
-        <v>25</v>
-      </c>
-      <c r="F221" t="s">
-        <v>35</v>
-      </c>
-      <c r="G221" t="s">
-        <v>498</v>
-      </c>
-      <c r="H221" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="222" spans="2:8">
-      <c r="B222" t="s">
-        <v>17</v>
-      </c>
-      <c r="C222" t="s">
-        <v>931</v>
-      </c>
-      <c r="D222" t="s">
-        <v>932</v>
-      </c>
-      <c r="E222" t="s">
-        <v>25</v>
-      </c>
-      <c r="F222" t="s">
-        <v>35</v>
-      </c>
-      <c r="G222" t="s">
-        <v>498</v>
-      </c>
-      <c r="H222" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="223" spans="2:8">
-      <c r="B223" t="s">
-        <v>17</v>
-      </c>
-      <c r="C223" t="s">
-        <v>933</v>
-      </c>
-      <c r="D223" t="s">
-        <v>934</v>
-      </c>
-      <c r="E223" t="s">
-        <v>25</v>
-      </c>
-      <c r="F223" t="s">
-        <v>35</v>
-      </c>
-      <c r="G223" t="s">
-        <v>498</v>
-      </c>
-      <c r="H223" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="224" spans="2:8">
-      <c r="B224" t="s">
-        <v>17</v>
-      </c>
-      <c r="C224" t="s">
-        <v>935</v>
-      </c>
-      <c r="D224" t="s">
-        <v>936</v>
-      </c>
-      <c r="E224" t="s">
-        <v>25</v>
-      </c>
-      <c r="F224" t="s">
-        <v>35</v>
-      </c>
-      <c r="G224" t="s">
-        <v>498</v>
-      </c>
-      <c r="H224" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="225" spans="2:8">
-      <c r="B225" t="s">
-        <v>17</v>
-      </c>
-      <c r="C225" t="s">
-        <v>937</v>
-      </c>
-      <c r="D225" t="s">
-        <v>938</v>
-      </c>
-      <c r="E225" t="s">
-        <v>25</v>
-      </c>
-      <c r="F225" t="s">
-        <v>35</v>
-      </c>
-      <c r="G225" t="s">
-        <v>498</v>
-      </c>
-      <c r="H225" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="226" spans="2:8">
-      <c r="B226" t="s">
-        <v>17</v>
-      </c>
-      <c r="C226" t="s">
-        <v>939</v>
-      </c>
-      <c r="D226" t="s">
-        <v>940</v>
-      </c>
-      <c r="E226" t="s">
-        <v>25</v>
-      </c>
-      <c r="F226" t="s">
-        <v>35</v>
-      </c>
-      <c r="G226" t="s">
-        <v>498</v>
-      </c>
-      <c r="H226" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="227" spans="2:8">
-      <c r="B227" t="s">
-        <v>17</v>
-      </c>
-      <c r="C227" t="s">
-        <v>941</v>
-      </c>
-      <c r="D227" t="s">
-        <v>942</v>
-      </c>
-      <c r="E227" t="s">
-        <v>25</v>
-      </c>
-      <c r="F227" t="s">
-        <v>35</v>
-      </c>
-      <c r="G227" t="s">
-        <v>498</v>
-      </c>
-      <c r="H227" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="228" spans="2:8">
-      <c r="B228" t="s">
-        <v>17</v>
-      </c>
-      <c r="C228" t="s">
-        <v>943</v>
-      </c>
-      <c r="D228" t="s">
-        <v>944</v>
-      </c>
-      <c r="E228" t="s">
-        <v>25</v>
-      </c>
-      <c r="F228" t="s">
-        <v>35</v>
-      </c>
-      <c r="G228" t="s">
-        <v>498</v>
-      </c>
-      <c r="H228" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="229" spans="2:8">
-      <c r="B229" t="s">
-        <v>17</v>
-      </c>
-      <c r="C229" t="s">
-        <v>945</v>
-      </c>
-      <c r="D229" t="s">
-        <v>946</v>
-      </c>
-      <c r="E229" t="s">
-        <v>25</v>
-      </c>
-      <c r="F229" t="s">
-        <v>35</v>
-      </c>
-      <c r="G229" t="s">
-        <v>498</v>
-      </c>
-      <c r="H229" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="230" spans="2:8">
-      <c r="B230" t="s">
-        <v>17</v>
-      </c>
-      <c r="C230" t="s">
-        <v>947</v>
-      </c>
-      <c r="D230" t="s">
-        <v>948</v>
-      </c>
-      <c r="E230" t="s">
-        <v>25</v>
-      </c>
-      <c r="F230" t="s">
-        <v>35</v>
-      </c>
-      <c r="G230" t="s">
-        <v>498</v>
-      </c>
-      <c r="H230" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="231" spans="2:8">
-      <c r="B231" t="s">
-        <v>17</v>
-      </c>
-      <c r="C231" t="s">
-        <v>949</v>
-      </c>
-      <c r="D231" t="s">
-        <v>950</v>
-      </c>
-      <c r="E231" t="s">
-        <v>25</v>
-      </c>
-      <c r="F231" t="s">
-        <v>35</v>
-      </c>
-      <c r="G231" t="s">
-        <v>498</v>
-      </c>
-      <c r="H231" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="232" spans="2:8">
-      <c r="B232" t="s">
-        <v>17</v>
-      </c>
-      <c r="C232" t="s">
-        <v>951</v>
-      </c>
-      <c r="D232" t="s">
-        <v>952</v>
-      </c>
-      <c r="E232" t="s">
-        <v>25</v>
-      </c>
-      <c r="F232" t="s">
-        <v>35</v>
-      </c>
-      <c r="G232" t="s">
-        <v>498</v>
-      </c>
-      <c r="H232" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="233" spans="2:8">
-      <c r="B233" t="s">
-        <v>17</v>
-      </c>
-      <c r="C233" t="s">
-        <v>953</v>
-      </c>
-      <c r="D233" t="s">
-        <v>954</v>
-      </c>
-      <c r="E233" t="s">
-        <v>25</v>
-      </c>
-      <c r="F233" t="s">
-        <v>35</v>
-      </c>
-      <c r="G233" t="s">
-        <v>498</v>
-      </c>
-      <c r="H233" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="234" spans="2:8">
-      <c r="B234" t="s">
-        <v>17</v>
-      </c>
-      <c r="C234" t="s">
-        <v>955</v>
-      </c>
-      <c r="D234" t="s">
-        <v>956</v>
-      </c>
-      <c r="E234" t="s">
-        <v>25</v>
-      </c>
-      <c r="F234" t="s">
-        <v>35</v>
-      </c>
-      <c r="G234" t="s">
-        <v>498</v>
-      </c>
-      <c r="H234" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="235" spans="2:8">
-      <c r="B235" t="s">
-        <v>17</v>
-      </c>
-      <c r="C235" t="s">
-        <v>957</v>
-      </c>
-      <c r="D235" t="s">
-        <v>958</v>
-      </c>
-      <c r="E235" t="s">
-        <v>25</v>
-      </c>
-      <c r="F235" t="s">
-        <v>35</v>
-      </c>
-      <c r="G235" t="s">
-        <v>498</v>
-      </c>
-      <c r="H235" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="236" spans="2:8">
-      <c r="B236" t="s">
-        <v>17</v>
-      </c>
-      <c r="C236" t="s">
-        <v>959</v>
-      </c>
-      <c r="D236" t="s">
-        <v>960</v>
-      </c>
-      <c r="E236" t="s">
-        <v>25</v>
-      </c>
-      <c r="F236" t="s">
-        <v>35</v>
-      </c>
-      <c r="G236" t="s">
-        <v>498</v>
-      </c>
-      <c r="H236" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="237" spans="2:8">
-      <c r="B237" t="s">
-        <v>17</v>
-      </c>
-      <c r="C237" t="s">
-        <v>961</v>
-      </c>
-      <c r="D237" t="s">
-        <v>962</v>
-      </c>
-      <c r="E237" t="s">
-        <v>25</v>
-      </c>
-      <c r="F237" t="s">
-        <v>35</v>
-      </c>
-      <c r="G237" t="s">
-        <v>498</v>
-      </c>
-      <c r="H237" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="238" spans="2:8">
-      <c r="B238" t="s">
-        <v>17</v>
-      </c>
-      <c r="C238" t="s">
-        <v>963</v>
-      </c>
-      <c r="D238" t="s">
-        <v>964</v>
-      </c>
-      <c r="E238" t="s">
-        <v>25</v>
-      </c>
-      <c r="F238" t="s">
-        <v>35</v>
-      </c>
-      <c r="G238" t="s">
-        <v>498</v>
-      </c>
-      <c r="H238" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="239" spans="2:8">
-      <c r="B239" t="s">
-        <v>17</v>
-      </c>
-      <c r="C239" t="s">
-        <v>965</v>
-      </c>
-      <c r="D239" t="s">
-        <v>966</v>
-      </c>
-      <c r="E239" t="s">
-        <v>25</v>
-      </c>
-      <c r="F239" t="s">
-        <v>35</v>
-      </c>
-      <c r="G239" t="s">
-        <v>498</v>
-      </c>
-      <c r="H239" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="240" spans="2:8">
-      <c r="B240" t="s">
-        <v>17</v>
-      </c>
-      <c r="C240" t="s">
-        <v>967</v>
-      </c>
-      <c r="D240" t="s">
-        <v>968</v>
-      </c>
-      <c r="E240" t="s">
-        <v>25</v>
-      </c>
-      <c r="F240" t="s">
-        <v>35</v>
-      </c>
-      <c r="G240" t="s">
-        <v>498</v>
-      </c>
-      <c r="H240" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="241" spans="2:8">
-      <c r="B241" t="s">
-        <v>17</v>
-      </c>
-      <c r="C241" t="s">
-        <v>969</v>
-      </c>
-      <c r="D241" t="s">
-        <v>970</v>
-      </c>
-      <c r="E241" t="s">
-        <v>25</v>
-      </c>
-      <c r="F241" t="s">
-        <v>35</v>
-      </c>
-      <c r="G241" t="s">
-        <v>498</v>
-      </c>
-      <c r="H241" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="242" spans="2:8">
-      <c r="B242" t="s">
-        <v>17</v>
-      </c>
-      <c r="C242" t="s">
-        <v>971</v>
-      </c>
-      <c r="D242" t="s">
-        <v>972</v>
-      </c>
-      <c r="E242" t="s">
-        <v>25</v>
-      </c>
-      <c r="F242" t="s">
-        <v>35</v>
-      </c>
-      <c r="G242" t="s">
-        <v>498</v>
-      </c>
-      <c r="H242" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="243" spans="2:8">
-      <c r="B243" t="s">
-        <v>17</v>
-      </c>
-      <c r="C243" t="s">
-        <v>973</v>
-      </c>
-      <c r="D243" t="s">
-        <v>974</v>
-      </c>
-      <c r="E243" t="s">
-        <v>25</v>
-      </c>
-      <c r="F243" t="s">
-        <v>35</v>
-      </c>
-      <c r="G243" t="s">
-        <v>498</v>
-      </c>
-      <c r="H243" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="244" spans="2:8">
-      <c r="B244" t="s">
-        <v>17</v>
-      </c>
-      <c r="C244" t="s">
-        <v>975</v>
-      </c>
-      <c r="D244" t="s">
-        <v>976</v>
-      </c>
-      <c r="E244" t="s">
-        <v>25</v>
-      </c>
-      <c r="F244" t="s">
-        <v>35</v>
-      </c>
-      <c r="G244" t="s">
-        <v>498</v>
-      </c>
-      <c r="H244" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="245" spans="2:8">
-      <c r="B245" t="s">
-        <v>17</v>
-      </c>
-      <c r="C245" t="s">
-        <v>977</v>
-      </c>
-      <c r="D245" t="s">
-        <v>978</v>
-      </c>
-      <c r="E245" t="s">
-        <v>25</v>
-      </c>
-      <c r="F245" t="s">
-        <v>35</v>
-      </c>
-      <c r="G245" t="s">
-        <v>498</v>
-      </c>
-      <c r="H245" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="246" spans="2:8">
-      <c r="B246" t="s">
-        <v>17</v>
-      </c>
-      <c r="C246" t="s">
-        <v>979</v>
-      </c>
-      <c r="D246" t="s">
-        <v>980</v>
-      </c>
-      <c r="E246" t="s">
-        <v>25</v>
-      </c>
-      <c r="F246" t="s">
-        <v>35</v>
-      </c>
-      <c r="G246" t="s">
-        <v>498</v>
-      </c>
-      <c r="H246" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="247" spans="2:8">
-      <c r="B247" t="s">
-        <v>17</v>
-      </c>
-      <c r="C247" t="s">
-        <v>981</v>
-      </c>
-      <c r="D247" t="s">
-        <v>982</v>
-      </c>
-      <c r="E247" t="s">
-        <v>25</v>
-      </c>
-      <c r="F247" t="s">
-        <v>35</v>
-      </c>
-      <c r="G247" t="s">
-        <v>498</v>
-      </c>
-      <c r="H247" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="248" spans="2:8">
-      <c r="B248" t="s">
-        <v>17</v>
-      </c>
-      <c r="C248" t="s">
-        <v>983</v>
-      </c>
-      <c r="D248" t="s">
-        <v>984</v>
-      </c>
-      <c r="E248" t="s">
-        <v>25</v>
-      </c>
-      <c r="F248" t="s">
-        <v>35</v>
-      </c>
-      <c r="G248" t="s">
-        <v>498</v>
-      </c>
-      <c r="H248" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="249" spans="2:8">
-      <c r="B249" t="s">
-        <v>17</v>
-      </c>
-      <c r="C249" t="s">
-        <v>985</v>
-      </c>
-      <c r="D249" t="s">
-        <v>986</v>
-      </c>
-      <c r="E249" t="s">
-        <v>25</v>
-      </c>
-      <c r="F249" t="s">
-        <v>35</v>
-      </c>
-      <c r="G249" t="s">
-        <v>498</v>
-      </c>
-      <c r="H249" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="250" spans="2:8">
-      <c r="B250" t="s">
-        <v>17</v>
-      </c>
-      <c r="C250" t="s">
-        <v>987</v>
-      </c>
-      <c r="D250" t="s">
-        <v>988</v>
-      </c>
-      <c r="E250" t="s">
-        <v>25</v>
-      </c>
-      <c r="F250" t="s">
-        <v>35</v>
-      </c>
-      <c r="G250" t="s">
-        <v>498</v>
-      </c>
-      <c r="H250" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="251" spans="2:8">
-      <c r="B251" t="s">
-        <v>17</v>
-      </c>
-      <c r="C251" t="s">
-        <v>989</v>
-      </c>
-      <c r="D251" t="s">
-        <v>990</v>
-      </c>
-      <c r="E251" t="s">
-        <v>25</v>
-      </c>
-      <c r="F251" t="s">
-        <v>35</v>
-      </c>
-      <c r="G251" t="s">
-        <v>498</v>
-      </c>
-      <c r="H251" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="252" spans="2:8">
-      <c r="B252" t="s">
-        <v>17</v>
-      </c>
-      <c r="C252" t="s">
-        <v>991</v>
-      </c>
-      <c r="D252" t="s">
-        <v>992</v>
-      </c>
-      <c r="E252" t="s">
-        <v>25</v>
-      </c>
-      <c r="F252" t="s">
-        <v>35</v>
-      </c>
-      <c r="G252" t="s">
-        <v>498</v>
-      </c>
-      <c r="H252" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="253" spans="2:8">
-      <c r="B253" t="s">
-        <v>17</v>
-      </c>
-      <c r="C253" t="s">
-        <v>993</v>
-      </c>
-      <c r="D253" t="s">
-        <v>994</v>
-      </c>
-      <c r="E253" t="s">
-        <v>25</v>
-      </c>
-      <c r="F253" t="s">
-        <v>35</v>
-      </c>
-      <c r="G253" t="s">
-        <v>498</v>
-      </c>
-      <c r="H253" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="254" spans="2:8">
-      <c r="B254" t="s">
-        <v>17</v>
-      </c>
-      <c r="C254" t="s">
-        <v>995</v>
-      </c>
-      <c r="D254" t="s">
-        <v>996</v>
-      </c>
-      <c r="E254" t="s">
-        <v>25</v>
-      </c>
-      <c r="F254" t="s">
-        <v>35</v>
-      </c>
-      <c r="G254" t="s">
-        <v>498</v>
-      </c>
-      <c r="H254" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="255" spans="2:8">
-      <c r="B255" t="s">
-        <v>17</v>
-      </c>
-      <c r="C255" t="s">
-        <v>997</v>
-      </c>
-      <c r="D255" t="s">
-        <v>998</v>
-      </c>
-      <c r="E255" t="s">
-        <v>25</v>
-      </c>
-      <c r="F255" t="s">
-        <v>35</v>
-      </c>
-      <c r="G255" t="s">
-        <v>498</v>
-      </c>
-      <c r="H255" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="256" spans="2:8">
-      <c r="B256" t="s">
-        <v>17</v>
-      </c>
-      <c r="C256" t="s">
-        <v>999</v>
-      </c>
-      <c r="D256" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E256" t="s">
-        <v>25</v>
-      </c>
-      <c r="F256" t="s">
-        <v>35</v>
-      </c>
-      <c r="G256" t="s">
-        <v>498</v>
-      </c>
-      <c r="H256" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="257" spans="2:8">
-      <c r="B257" t="s">
-        <v>17</v>
-      </c>
-      <c r="C257" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D257" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E257" t="s">
-        <v>25</v>
-      </c>
-      <c r="F257" t="s">
-        <v>35</v>
-      </c>
-      <c r="G257" t="s">
-        <v>498</v>
-      </c>
-      <c r="H257" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="258" spans="2:8">
-      <c r="B258" t="s">
-        <v>17</v>
-      </c>
-      <c r="C258" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D258" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E258" t="s">
-        <v>25</v>
-      </c>
-      <c r="F258" t="s">
-        <v>35</v>
-      </c>
-      <c r="G258" t="s">
-        <v>498</v>
-      </c>
-      <c r="H258" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="259" spans="2:8">
-      <c r="B259" t="s">
-        <v>17</v>
-      </c>
-      <c r="C259" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D259" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E259" t="s">
-        <v>25</v>
-      </c>
-      <c r="F259" t="s">
-        <v>35</v>
-      </c>
-      <c r="G259" t="s">
-        <v>498</v>
-      </c>
-      <c r="H259" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="260" spans="2:8">
-      <c r="B260" t="s">
-        <v>17</v>
-      </c>
-      <c r="C260" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D260" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E260" t="s">
-        <v>25</v>
-      </c>
-      <c r="F260" t="s">
-        <v>35</v>
-      </c>
-      <c r="G260" t="s">
-        <v>498</v>
-      </c>
-      <c r="H260" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="261" spans="2:8">
-      <c r="B261" t="s">
-        <v>17</v>
-      </c>
-      <c r="C261" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D261" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E261" t="s">
-        <v>25</v>
-      </c>
-      <c r="F261" t="s">
-        <v>35</v>
-      </c>
-      <c r="G261" t="s">
-        <v>498</v>
-      </c>
-      <c r="H261" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="262" spans="2:8">
-      <c r="B262" t="s">
-        <v>17</v>
-      </c>
-      <c r="C262" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D262" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E262" t="s">
-        <v>25</v>
-      </c>
-      <c r="F262" t="s">
-        <v>35</v>
-      </c>
-      <c r="G262" t="s">
-        <v>498</v>
-      </c>
-      <c r="H262" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="263" spans="2:8">
-      <c r="B263" t="s">
-        <v>17</v>
-      </c>
-      <c r="C263" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D263" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E263" t="s">
-        <v>25</v>
-      </c>
-      <c r="F263" t="s">
-        <v>35</v>
-      </c>
-      <c r="G263" t="s">
-        <v>498</v>
-      </c>
-      <c r="H263" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="264" spans="2:8">
-      <c r="B264" t="s">
-        <v>17</v>
-      </c>
-      <c r="C264" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E264" t="s">
-        <v>25</v>
-      </c>
-      <c r="F264" t="s">
-        <v>35</v>
-      </c>
-      <c r="G264" t="s">
-        <v>498</v>
-      </c>
-      <c r="H264" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="265" spans="2:8">
-      <c r="B265" t="s">
-        <v>17</v>
-      </c>
-      <c r="C265" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D265" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E265" t="s">
-        <v>25</v>
-      </c>
-      <c r="F265" t="s">
-        <v>35</v>
-      </c>
-      <c r="G265" t="s">
-        <v>498</v>
-      </c>
-      <c r="H265" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="266" spans="2:8">
-      <c r="B266" t="s">
-        <v>17</v>
-      </c>
-      <c r="C266" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D266" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E266" t="s">
-        <v>25</v>
-      </c>
-      <c r="F266" t="s">
-        <v>35</v>
-      </c>
-      <c r="G266" t="s">
-        <v>498</v>
-      </c>
-      <c r="H266" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="267" spans="2:8">
-      <c r="B267" t="s">
-        <v>17</v>
-      </c>
-      <c r="C267" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D267" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E267" t="s">
-        <v>25</v>
-      </c>
-      <c r="F267" t="s">
-        <v>35</v>
-      </c>
-      <c r="G267" t="s">
-        <v>498</v>
-      </c>
-      <c r="H267" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="268" spans="2:8">
-      <c r="B268" t="s">
-        <v>17</v>
-      </c>
-      <c r="C268" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D268" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E268" t="s">
-        <v>25</v>
-      </c>
-      <c r="F268" t="s">
-        <v>35</v>
-      </c>
-      <c r="G268" t="s">
-        <v>498</v>
-      </c>
-      <c r="H268" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="269" spans="2:8">
-      <c r="B269" t="s">
-        <v>17</v>
-      </c>
-      <c r="C269" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D269" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E269" t="s">
-        <v>25</v>
-      </c>
-      <c r="F269" t="s">
-        <v>35</v>
-      </c>
-      <c r="G269" t="s">
-        <v>498</v>
-      </c>
-      <c r="H269" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="270" spans="2:8">
-      <c r="B270" t="s">
-        <v>17</v>
-      </c>
-      <c r="C270" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D270" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E270" t="s">
-        <v>25</v>
-      </c>
-      <c r="F270" t="s">
-        <v>35</v>
-      </c>
-      <c r="G270" t="s">
-        <v>498</v>
-      </c>
-      <c r="H270" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="271" spans="2:8">
-      <c r="B271" t="s">
-        <v>17</v>
-      </c>
-      <c r="C271" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D271" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E271" t="s">
-        <v>25</v>
-      </c>
-      <c r="F271" t="s">
-        <v>35</v>
-      </c>
-      <c r="G271" t="s">
-        <v>498</v>
-      </c>
-      <c r="H271" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="272" spans="2:8">
-      <c r="B272" t="s">
-        <v>17</v>
-      </c>
-      <c r="C272" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D272" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E272" t="s">
-        <v>25</v>
-      </c>
-      <c r="F272" t="s">
-        <v>35</v>
-      </c>
-      <c r="G272" t="s">
-        <v>498</v>
-      </c>
-      <c r="H272" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="273" spans="2:8">
-      <c r="B273" t="s">
-        <v>17</v>
-      </c>
-      <c r="C273" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D273" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E273" t="s">
-        <v>25</v>
-      </c>
-      <c r="F273" t="s">
-        <v>35</v>
-      </c>
-      <c r="G273" t="s">
-        <v>498</v>
-      </c>
-      <c r="H273" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="274" spans="2:8">
-      <c r="B274" t="s">
-        <v>17</v>
-      </c>
-      <c r="C274" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D274" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E274" t="s">
-        <v>25</v>
-      </c>
-      <c r="F274" t="s">
-        <v>35</v>
-      </c>
-      <c r="G274" t="s">
-        <v>498</v>
-      </c>
-      <c r="H274" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="275" spans="2:8">
-      <c r="B275" t="s">
-        <v>17</v>
-      </c>
-      <c r="C275" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D275" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E275" t="s">
-        <v>25</v>
-      </c>
-      <c r="F275" t="s">
-        <v>35</v>
-      </c>
-      <c r="G275" t="s">
-        <v>498</v>
-      </c>
-      <c r="H275" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="276" spans="2:8">
-      <c r="B276" t="s">
-        <v>17</v>
-      </c>
-      <c r="C276" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D276" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E276" t="s">
-        <v>25</v>
-      </c>
-      <c r="F276" t="s">
-        <v>35</v>
-      </c>
-      <c r="G276" t="s">
-        <v>498</v>
-      </c>
-      <c r="H276" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="277" spans="2:8">
-      <c r="B277" t="s">
-        <v>17</v>
-      </c>
-      <c r="C277" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D277" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E277" t="s">
-        <v>25</v>
-      </c>
-      <c r="F277" t="s">
-        <v>35</v>
-      </c>
-      <c r="G277" t="s">
-        <v>498</v>
-      </c>
-      <c r="H277" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="278" spans="2:8">
-      <c r="B278" t="s">
-        <v>17</v>
-      </c>
-      <c r="C278" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D278" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E278" t="s">
-        <v>25</v>
-      </c>
-      <c r="F278" t="s">
-        <v>35</v>
-      </c>
-      <c r="G278" t="s">
-        <v>498</v>
-      </c>
-      <c r="H278" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="279" spans="2:8">
-      <c r="B279" t="s">
-        <v>17</v>
-      </c>
-      <c r="C279" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D279" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E279" t="s">
-        <v>25</v>
-      </c>
-      <c r="F279" t="s">
-        <v>35</v>
-      </c>
-      <c r="G279" t="s">
-        <v>498</v>
-      </c>
-      <c r="H279" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="280" spans="2:8">
-      <c r="B280" t="s">
-        <v>17</v>
-      </c>
-      <c r="C280" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D280" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E280" t="s">
-        <v>25</v>
-      </c>
-      <c r="F280" t="s">
-        <v>35</v>
-      </c>
-      <c r="G280" t="s">
-        <v>498</v>
-      </c>
-      <c r="H280" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="281" spans="2:8">
-      <c r="B281" t="s">
-        <v>17</v>
-      </c>
-      <c r="C281" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D281" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E281" t="s">
-        <v>25</v>
-      </c>
-      <c r="F281" t="s">
-        <v>35</v>
-      </c>
-      <c r="G281" t="s">
-        <v>498</v>
-      </c>
-      <c r="H281" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="282" spans="2:8">
-      <c r="B282" t="s">
-        <v>17</v>
-      </c>
-      <c r="C282" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E282" t="s">
-        <v>25</v>
-      </c>
-      <c r="F282" t="s">
-        <v>35</v>
-      </c>
-      <c r="G282" t="s">
-        <v>498</v>
-      </c>
-      <c r="H282" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="283" spans="2:8">
-      <c r="B283" t="s">
-        <v>17</v>
-      </c>
-      <c r="C283" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D283" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E283" t="s">
-        <v>25</v>
-      </c>
-      <c r="F283" t="s">
-        <v>35</v>
-      </c>
-      <c r="G283" t="s">
-        <v>498</v>
-      </c>
-      <c r="H283" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="284" spans="2:8">
-      <c r="B284" t="s">
-        <v>17</v>
-      </c>
-      <c r="C284" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D284" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E284" t="s">
-        <v>25</v>
-      </c>
-      <c r="F284" t="s">
-        <v>35</v>
-      </c>
-      <c r="G284" t="s">
-        <v>498</v>
-      </c>
-      <c r="H284" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="285" spans="2:8">
-      <c r="B285" t="s">
-        <v>17</v>
-      </c>
-      <c r="C285" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D285" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E285" t="s">
-        <v>25</v>
-      </c>
-      <c r="F285" t="s">
-        <v>35</v>
-      </c>
-      <c r="G285" t="s">
-        <v>498</v>
-      </c>
-      <c r="H285" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="286" spans="2:8">
-      <c r="B286" t="s">
-        <v>17</v>
-      </c>
-      <c r="C286" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D286" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E286" t="s">
-        <v>25</v>
-      </c>
-      <c r="F286" t="s">
-        <v>35</v>
-      </c>
-      <c r="G286" t="s">
-        <v>498</v>
-      </c>
-      <c r="H286" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="287" spans="2:8">
-      <c r="B287" t="s">
-        <v>17</v>
-      </c>
-      <c r="C287" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D287" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E287" t="s">
-        <v>25</v>
-      </c>
-      <c r="F287" t="s">
-        <v>35</v>
-      </c>
-      <c r="G287" t="s">
-        <v>498</v>
-      </c>
-      <c r="H287" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="288" spans="2:8">
-      <c r="B288" t="s">
-        <v>17</v>
-      </c>
-      <c r="C288" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D288" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E288" t="s">
-        <v>25</v>
-      </c>
-      <c r="F288" t="s">
-        <v>35</v>
-      </c>
-      <c r="G288" t="s">
-        <v>498</v>
-      </c>
-      <c r="H288" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="289" spans="2:8">
-      <c r="B289" t="s">
-        <v>17</v>
-      </c>
-      <c r="C289" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D289" t="s">
-        <v>1066</v>
-      </c>
-      <c r="E289" t="s">
-        <v>25</v>
-      </c>
-      <c r="F289" t="s">
-        <v>35</v>
-      </c>
-      <c r="G289" t="s">
-        <v>498</v>
-      </c>
-      <c r="H289" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="290" spans="2:8">
-      <c r="B290" t="s">
-        <v>17</v>
-      </c>
-      <c r="C290" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D290" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E290" t="s">
-        <v>25</v>
-      </c>
-      <c r="F290" t="s">
-        <v>35</v>
-      </c>
-      <c r="G290" t="s">
-        <v>498</v>
-      </c>
-      <c r="H290" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="291" spans="2:8">
-      <c r="B291" t="s">
-        <v>17</v>
-      </c>
-      <c r="C291" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D291" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E291" t="s">
-        <v>25</v>
-      </c>
-      <c r="F291" t="s">
-        <v>35</v>
-      </c>
-      <c r="G291" t="s">
-        <v>498</v>
-      </c>
-      <c r="H291" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="292" spans="2:8">
-      <c r="B292" t="s">
-        <v>17</v>
-      </c>
-      <c r="C292" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D292" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E292" t="s">
-        <v>25</v>
-      </c>
-      <c r="F292" t="s">
-        <v>35</v>
-      </c>
-      <c r="G292" t="s">
-        <v>498</v>
-      </c>
-      <c r="H292" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="293" spans="2:8">
-      <c r="B293" t="s">
-        <v>17</v>
-      </c>
-      <c r="C293" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D293" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E293" t="s">
-        <v>25</v>
-      </c>
-      <c r="F293" t="s">
-        <v>35</v>
-      </c>
-      <c r="G293" t="s">
-        <v>498</v>
-      </c>
-      <c r="H293" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="294" spans="2:8">
-      <c r="B294" t="s">
-        <v>17</v>
-      </c>
-      <c r="C294" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D294" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E294" t="s">
-        <v>25</v>
-      </c>
-      <c r="F294" t="s">
-        <v>35</v>
-      </c>
-      <c r="G294" t="s">
-        <v>498</v>
-      </c>
-      <c r="H294" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="295" spans="2:8">
-      <c r="B295" t="s">
-        <v>17</v>
-      </c>
-      <c r="C295" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D295" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E295" t="s">
-        <v>25</v>
-      </c>
-      <c r="F295" t="s">
-        <v>35</v>
-      </c>
-      <c r="G295" t="s">
-        <v>498</v>
-      </c>
-      <c r="H295" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="296" spans="2:8">
-      <c r="B296" t="s">
-        <v>17</v>
-      </c>
-      <c r="C296" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D296" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E296" t="s">
-        <v>25</v>
-      </c>
-      <c r="F296" t="s">
-        <v>35</v>
-      </c>
-      <c r="G296" t="s">
-        <v>498</v>
-      </c>
-      <c r="H296" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="297" spans="2:8">
-      <c r="B297" t="s">
-        <v>17</v>
-      </c>
-      <c r="C297" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D297" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E297" t="s">
-        <v>25</v>
-      </c>
-      <c r="F297" t="s">
-        <v>35</v>
-      </c>
-      <c r="G297" t="s">
-        <v>498</v>
-      </c>
-      <c r="H297" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="298" spans="2:8">
-      <c r="B298" t="s">
-        <v>17</v>
-      </c>
-      <c r="C298" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D298" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E298" t="s">
-        <v>25</v>
-      </c>
-      <c r="F298" t="s">
-        <v>35</v>
-      </c>
-      <c r="G298" t="s">
-        <v>498</v>
-      </c>
-      <c r="H298" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="299" spans="2:8">
-      <c r="B299" t="s">
-        <v>17</v>
-      </c>
-      <c r="C299" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D299" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E299" t="s">
-        <v>25</v>
-      </c>
-      <c r="F299" t="s">
-        <v>35</v>
-      </c>
-      <c r="G299" t="s">
-        <v>498</v>
-      </c>
-      <c r="H299" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="300" spans="2:8">
-      <c r="B300" t="s">
-        <v>17</v>
-      </c>
-      <c r="C300" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D300" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E300" t="s">
-        <v>25</v>
-      </c>
-      <c r="F300" t="s">
-        <v>35</v>
-      </c>
-      <c r="G300" t="s">
-        <v>498</v>
-      </c>
-      <c r="H300" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="301" spans="2:8">
-      <c r="B301" t="s">
-        <v>17</v>
-      </c>
-      <c r="C301" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D301" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E301" t="s">
-        <v>25</v>
-      </c>
-      <c r="F301" t="s">
-        <v>35</v>
-      </c>
-      <c r="G301" t="s">
-        <v>498</v>
-      </c>
-      <c r="H301" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="302" spans="2:8">
-      <c r="B302" t="s">
-        <v>17</v>
-      </c>
-      <c r="C302" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D302" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E302" t="s">
-        <v>25</v>
-      </c>
-      <c r="F302" t="s">
-        <v>35</v>
-      </c>
-      <c r="G302" t="s">
-        <v>498</v>
-      </c>
-      <c r="H302" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="303" spans="2:8">
-      <c r="B303" t="s">
-        <v>17</v>
-      </c>
-      <c r="C303" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D303" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E303" t="s">
-        <v>25</v>
-      </c>
-      <c r="F303" t="s">
-        <v>35</v>
-      </c>
-      <c r="G303" t="s">
-        <v>498</v>
-      </c>
-      <c r="H303" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="304" spans="2:8">
-      <c r="B304" t="s">
-        <v>17</v>
-      </c>
-      <c r="C304" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D304" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E304" t="s">
-        <v>25</v>
-      </c>
-      <c r="F304" t="s">
-        <v>35</v>
-      </c>
-      <c r="G304" t="s">
-        <v>498</v>
-      </c>
-      <c r="H304" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="305" spans="2:8">
-      <c r="B305" t="s">
-        <v>17</v>
-      </c>
-      <c r="C305" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D305" t="s">
-        <v>1098</v>
-      </c>
-      <c r="E305" t="s">
-        <v>25</v>
-      </c>
-      <c r="F305" t="s">
-        <v>35</v>
-      </c>
-      <c r="G305" t="s">
-        <v>498</v>
-      </c>
-      <c r="H305" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="306" spans="2:8">
-      <c r="B306" t="s">
-        <v>17</v>
-      </c>
-      <c r="C306" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D306" t="s">
-        <v>1100</v>
-      </c>
-      <c r="E306" t="s">
-        <v>25</v>
-      </c>
-      <c r="F306" t="s">
-        <v>35</v>
-      </c>
-      <c r="G306" t="s">
-        <v>498</v>
-      </c>
-      <c r="H306" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="307" spans="2:8">
-      <c r="B307" t="s">
-        <v>17</v>
-      </c>
-      <c r="C307" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D307" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E307" t="s">
-        <v>25</v>
-      </c>
-      <c r="F307" t="s">
-        <v>35</v>
-      </c>
-      <c r="G307" t="s">
-        <v>498</v>
-      </c>
-      <c r="H307" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="308" spans="2:8">
-      <c r="B308" t="s">
-        <v>17</v>
-      </c>
-      <c r="C308" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D308" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E308" t="s">
-        <v>25</v>
-      </c>
-      <c r="F308" t="s">
-        <v>35</v>
-      </c>
-      <c r="G308" t="s">
-        <v>498</v>
-      </c>
-      <c r="H308" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="309" spans="2:8">
-      <c r="B309" t="s">
-        <v>17</v>
-      </c>
-      <c r="C309" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D309" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E309" t="s">
-        <v>25</v>
-      </c>
-      <c r="F309" t="s">
-        <v>35</v>
-      </c>
-      <c r="G309" t="s">
-        <v>498</v>
-      </c>
-      <c r="H309" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="310" spans="2:8">
-      <c r="B310" t="s">
-        <v>17</v>
-      </c>
-      <c r="C310" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D310" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E310" t="s">
-        <v>25</v>
-      </c>
-      <c r="F310" t="s">
-        <v>35</v>
-      </c>
-      <c r="G310" t="s">
-        <v>498</v>
-      </c>
-      <c r="H310" t="s">
         <v>216</v>
       </c>
     </row>

--- a/VerveStacks_DZA_grids/SysSettings.xlsx
+++ b/VerveStacks_DZA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D46639-6FC2-460C-B2AE-C3D24F8E1F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24966F26-B4B8-46B9-8814-BF3ECFBB8B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4232,7 +4232,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB85B8EC-E129-47CF-93E5-E6427F50AF9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57BCB28-D7EC-4840-9FE8-0E52DAA37DF7}">
   <dimension ref="B3:H52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SysSettings.xlsx
+++ b/VerveStacks_DZA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24966F26-B4B8-46B9-8814-BF3ECFBB8B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDE2964-11FF-4FB5-998B-B5493FCBFD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4232,7 +4232,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57BCB28-D7EC-4840-9FE8-0E52DAA37DF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C0BFB7-6EBD-46C3-ABE8-7952C52DD413}">
   <dimension ref="B3:H52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
